--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13304,7 +13304,7 @@
         <v>127684093</v>
       </c>
       <c r="B100" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>128162622</v>
       </c>
       <c r="B101" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>128162411</v>
       </c>
       <c r="B102" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>127945591</v>
       </c>
       <c r="B103" t="n">
-        <v>57558</v>
+        <v>57570</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13798,6 +13798,568 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128527516</v>
+      </c>
+      <c r="B104" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Salsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>561159</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6627762</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128527505</v>
+      </c>
+      <c r="B105" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Salsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>561131</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6627744</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128527567</v>
+      </c>
+      <c r="B106" t="n">
+        <v>90289</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6292</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tricholoma viridilutescens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Salsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>561125</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6627715</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128527532</v>
+      </c>
+      <c r="B107" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Salsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>561177</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6627773</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128527542</v>
+      </c>
+      <c r="B108" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Salsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>561174</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6627743</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B106" t="n">
-        <v>90289</v>
+        <v>92742</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,25 +14040,33 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14067,10 +14075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R106" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14135,10 +14143,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B107" t="n">
-        <v>92742</v>
+        <v>90289</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14146,33 +14154,25 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R107" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14361,6 +14361,565 @@
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128646385</v>
+      </c>
+      <c r="B109" t="n">
+        <v>92743</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Murmossen O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>561118</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6627266</v>
+      </c>
+      <c r="S109" t="n">
+        <v>25</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128646464</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92755</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Murmossen O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6627403</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog i mosskant</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128646469</v>
+      </c>
+      <c r="B111" t="n">
+        <v>90290</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6292</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Tricholoma viridilutescens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Murmossen O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6627403</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog i mosskant</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128646412</v>
+      </c>
+      <c r="B112" t="n">
+        <v>92779</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Murmossen O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>560935</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6627395</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog i mosskant</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128646439</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91418</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Murmossen O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>560935</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6627395</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog i mosskant</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B106" t="n">
-        <v>92742</v>
+        <v>90295</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,33 +14040,25 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14075,10 +14067,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R106" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14143,10 +14135,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B107" t="n">
-        <v>90289</v>
+        <v>92748</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14154,25 +14146,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R107" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92755</v>
+        <v>92760</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90290</v>
+        <v>90295</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92779</v>
+        <v>92784</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91418</v>
+        <v>91423</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13432,7 +13432,7 @@
         <v>128162622</v>
       </c>
       <c r="B101" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>128162411</v>
       </c>
       <c r="B102" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>127945591</v>
       </c>
       <c r="B103" t="n">
-        <v>57570</v>
+        <v>57574</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B106" t="n">
-        <v>90295</v>
+        <v>92754</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,25 +14040,33 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14067,10 +14075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R106" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14135,10 +14143,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B107" t="n">
-        <v>92748</v>
+        <v>90301</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14146,33 +14154,25 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R107" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90295</v>
+        <v>90301</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13432,7 +13432,7 @@
         <v>128162622</v>
       </c>
       <c r="B101" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>128162411</v>
       </c>
       <c r="B102" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B106" t="n">
-        <v>92754</v>
+        <v>90303</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,33 +14040,25 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14075,10 +14067,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R106" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14143,10 +14135,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B107" t="n">
-        <v>90301</v>
+        <v>92756</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14154,25 +14146,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R107" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90301</v>
+        <v>90303</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B106" t="n">
-        <v>90303</v>
+        <v>92756</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,25 +14040,33 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14067,10 +14075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R106" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14135,10 +14143,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B107" t="n">
-        <v>92756</v>
+        <v>90303</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14146,33 +14154,25 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R107" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14920,6 +14920,372 @@
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128758942</v>
+      </c>
+      <c r="B114" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Salsmosseskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>561152</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6627765</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128759184</v>
+      </c>
+      <c r="B115" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Salsmosseskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>561162</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6627767</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128759865</v>
+      </c>
+      <c r="B116" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>561210</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6627694</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13432,7 +13432,7 @@
         <v>128162622</v>
       </c>
       <c r="B101" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>128162411</v>
       </c>
       <c r="B102" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B106" t="n">
-        <v>92756</v>
+        <v>90303</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,33 +14040,25 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14075,10 +14067,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R106" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14143,10 +14135,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B107" t="n">
-        <v>90303</v>
+        <v>92757</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14154,25 +14146,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R107" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>128527567</v>
       </c>
       <c r="B106" t="n">
-        <v>90303</v>
+        <v>90330</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>128527532</v>
       </c>
       <c r="B107" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90303</v>
+        <v>90330</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13677,7 +13677,7 @@
         <v>127945591</v>
       </c>
       <c r="B103" t="n">
-        <v>57574</v>
+        <v>57601</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128527567</v>
+        <v>128527532</v>
       </c>
       <c r="B106" t="n">
-        <v>90330</v>
+        <v>92784</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14040,25 +14040,33 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -14067,10 +14075,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>561125</v>
+        <v>561177</v>
       </c>
       <c r="R106" t="n">
-        <v>6627715</v>
+        <v>6627773</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14135,10 +14143,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128527532</v>
+        <v>128527567</v>
       </c>
       <c r="B107" t="n">
-        <v>92784</v>
+        <v>90330</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14146,33 +14154,25 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>561177</v>
+        <v>561125</v>
       </c>
       <c r="R107" t="n">
-        <v>6627773</v>
+        <v>6627715</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>128527532</v>
       </c>
       <c r="B106" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>128527567</v>
       </c>
       <c r="B107" t="n">
-        <v>90330</v>
+        <v>90335</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90330</v>
+        <v>90335</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -13804,7 +13804,7 @@
         <v>128527516</v>
       </c>
       <c r="B104" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128527505</v>
       </c>
       <c r="B105" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>128527532</v>
       </c>
       <c r="B106" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>128527567</v>
       </c>
       <c r="B107" t="n">
-        <v>90351</v>
+        <v>90356</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>128527542</v>
       </c>
       <c r="B108" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90351</v>
+        <v>90356</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91480</v>
+        <v>91485</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -14925,7 +14925,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90356</v>
+        <v>90362</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91485</v>
+        <v>91491</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -14366,7 +14366,7 @@
         <v>128646385</v>
       </c>
       <c r="B109" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>128646464</v>
       </c>
       <c r="B110" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>128646469</v>
       </c>
       <c r="B111" t="n">
-        <v>90362</v>
+        <v>90366</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>128646412</v>
       </c>
       <c r="B112" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>128646439</v>
       </c>
       <c r="B113" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4133,15 +4133,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110818218</v>
+        <v>129294401</v>
       </c>
       <c r="B29" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4167,28 +4162,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Salsmossen, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561104.9095333075</v>
+        <v>561104</v>
       </c>
       <c r="R29" t="n">
-        <v>6627875.317932388</v>
+        <v>6627876</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4212,22 +4198,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4236,29 +4222,23 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Tall</t>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -15286,6 +15266,355 @@
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129294087</v>
+      </c>
+      <c r="B117" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>561103</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6627849</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129294690</v>
+      </c>
+      <c r="B118" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>561104</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6627876</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129294056</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>561078</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6627826</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Tall som fallit på Salsmossen</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -14905,7 +14905,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -14905,7 +14905,7 @@
         <v>128758942</v>
       </c>
       <c r="B114" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>128759184</v>
       </c>
       <c r="B115" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15615,6 +15615,513 @@
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129344316</v>
+      </c>
+      <c r="B120" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>561215</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6627683</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129344266</v>
+      </c>
+      <c r="B121" t="n">
+        <v>58370</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>561215</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6627683</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129344006</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>561189</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6627651</v>
+      </c>
+      <c r="S122" t="n">
+        <v>50</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129344132</v>
+      </c>
+      <c r="B123" t="n">
+        <v>57721</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>561150</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6627640</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15150,7 +15150,7 @@
         <v>128759865</v>
       </c>
       <c r="B116" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15873,32 +15873,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344006</v>
+        <v>129344132</v>
       </c>
       <c r="B122" t="n">
-        <v>57887</v>
+        <v>57721</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -15920,17 +15920,17 @@
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>561189</v>
+        <v>561150</v>
       </c>
       <c r="R122" t="n">
-        <v>6627651</v>
+        <v>6627640</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15980,6 +15980,11 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
@@ -15996,32 +16001,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344132</v>
+        <v>129344006</v>
       </c>
       <c r="B123" t="n">
-        <v>57721</v>
+        <v>57887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -16043,17 +16048,17 @@
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogsmuren, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>561150</v>
+        <v>561174</v>
       </c>
       <c r="R123" t="n">
-        <v>6627640</v>
+        <v>6627633</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -16082,7 +16087,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16092,7 +16097,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16103,11 +16108,6 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15617,27 +15617,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B120" t="n">
-        <v>58097</v>
+        <v>58370</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15745,27 +15745,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B121" t="n">
-        <v>58370</v>
+        <v>58097</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15873,32 +15873,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344132</v>
+        <v>129344006</v>
       </c>
       <c r="B122" t="n">
-        <v>57721</v>
+        <v>57887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -15920,17 +15920,17 @@
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogsmuren, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>561150</v>
+        <v>561174</v>
       </c>
       <c r="R122" t="n">
-        <v>6627640</v>
+        <v>6627633</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15980,11 +15980,6 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
@@ -16001,32 +15996,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344006</v>
+        <v>129344132</v>
       </c>
       <c r="B123" t="n">
-        <v>57887</v>
+        <v>57721</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -16048,17 +16043,17 @@
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Skogsmuren, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>561174</v>
+        <v>561150</v>
       </c>
       <c r="R123" t="n">
-        <v>6627633</v>
+        <v>6627640</v>
       </c>
       <c r="S123" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -16087,7 +16082,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16097,7 +16092,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16108,6 +16103,11 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15617,27 +15617,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B120" t="n">
-        <v>58370</v>
+        <v>58097</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15745,27 +15745,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B121" t="n">
-        <v>58097</v>
+        <v>58370</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15271,7 +15271,7 @@
         <v>129294087</v>
       </c>
       <c r="B117" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>129294690</v>
       </c>
       <c r="B118" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15617,27 +15617,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B120" t="n">
-        <v>58097</v>
+        <v>58370</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15745,27 +15745,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B121" t="n">
-        <v>58370</v>
+        <v>58097</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15617,27 +15617,27 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B120" t="n">
-        <v>58370</v>
+        <v>58097</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15745,27 +15745,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B121" t="n">
-        <v>58097</v>
+        <v>58370</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15405,7 +15405,7 @@
         <v>129294087</v>
       </c>
       <c r="B118" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>129294690</v>
       </c>
       <c r="B119" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15751,27 +15751,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B121" t="n">
-        <v>58370</v>
+        <v>58097</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B122" t="n">
-        <v>58097</v>
+        <v>58370</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -926,32 +926,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129544884</v>
+        <v>129599492</v>
       </c>
       <c r="B4" t="n">
-        <v>57585</v>
+        <v>57721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100137</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,20 +966,24 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
+          <t>Skogsmuren, naturbeteshagen. Ramnäs, Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561045</v>
+        <v>561041</v>
       </c>
       <c r="R4" t="n">
-        <v>6628113</v>
+        <v>6628105</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,27 +1007,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Satt i träd vid kanten i naturbeteshagen, har hörts och setts födosöka i området flertal gånger. Skrämdes o flög riktning N.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,11 +1037,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Naturbeteshage</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,32 +1054,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129599492</v>
+        <v>129544884</v>
       </c>
       <c r="B5" t="n">
-        <v>57721</v>
+        <v>57585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>100137</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1100,24 +1094,20 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogsmuren, naturbeteshagen. Ramnäs, Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
+          <t>Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561041</v>
+        <v>561045</v>
       </c>
       <c r="R5" t="n">
-        <v>6628105</v>
+        <v>6628113</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,22 +1131,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt i träd vid kanten i naturbeteshagen, har hörts och setts födosöka i området flertal gånger. Skrämdes o flög riktning N.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,6 +1166,11 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Naturbeteshage</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B122" t="n">
-        <v>58097</v>
+        <v>58370</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16007,27 +16007,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B123" t="n">
-        <v>58370</v>
+        <v>58097</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129599492</v>
       </c>
       <c r="B4" t="n">
-        <v>57721</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129544884</v>
       </c>
       <c r="B5" t="n">
-        <v>57585</v>
+        <v>57588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>129294087</v>
       </c>
       <c r="B119" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>129294690</v>
       </c>
       <c r="B120" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B122" t="n">
-        <v>58370</v>
+        <v>58100</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16007,27 +16007,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B123" t="n">
-        <v>58097</v>
+        <v>58373</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16138,7 +16138,7 @@
         <v>129344006</v>
       </c>
       <c r="B124" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>129344132</v>
       </c>
       <c r="B125" t="n">
-        <v>57721</v>
+        <v>57724</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16384,6 +16384,122 @@
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129681811</v>
+      </c>
+      <c r="B126" t="n">
+        <v>56705</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>560946</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6627396</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -926,32 +926,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129599492</v>
+        <v>129544884</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>100137</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -966,24 +966,20 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsmuren, naturbeteshagen. Ramnäs, Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
+          <t>Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561041</v>
+        <v>561045</v>
       </c>
       <c r="R4" t="n">
-        <v>6628105</v>
+        <v>6628113</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,22 +1003,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Satt i träd vid kanten i naturbeteshagen, har hörts och setts födosöka i området flertal gånger. Skrämdes o flög riktning N.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,6 +1038,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Naturbeteshage</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,32 +1060,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129544884</v>
+        <v>129599492</v>
       </c>
       <c r="B5" t="n">
-        <v>57588</v>
+        <v>57729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100137</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1094,20 +1100,24 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
+          <t>Skogsmuren, naturbeteshagen. Ramnäs, Skogsmuren, naturbeteshagen. Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561045</v>
+        <v>561041</v>
       </c>
       <c r="R5" t="n">
-        <v>6628113</v>
+        <v>6628105</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,27 +1141,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Satt i träd vid kanten i naturbeteshagen, har hörts och setts födosöka i området flertal gånger. Skrämdes o flög riktning N.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,11 +1171,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Naturbeteshage</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
         <v>129294087</v>
       </c>
       <c r="B119" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>129294690</v>
       </c>
       <c r="B120" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B122" t="n">
-        <v>58100</v>
+        <v>58378</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16007,27 +16007,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B123" t="n">
-        <v>58373</v>
+        <v>58105</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16138,7 +16138,7 @@
         <v>129344006</v>
       </c>
       <c r="B124" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>129344132</v>
       </c>
       <c r="B125" t="n">
-        <v>57724</v>
+        <v>57729</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>129681811</v>
       </c>
       <c r="B126" t="n">
-        <v>56705</v>
+        <v>56709</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129544884</v>
       </c>
       <c r="B4" t="n">
-        <v>57593</v>
+        <v>57594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>129599492</v>
       </c>
       <c r="B5" t="n">
-        <v>57729</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>129294087</v>
       </c>
       <c r="B119" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>129294690</v>
       </c>
       <c r="B120" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B122" t="n">
-        <v>58378</v>
+        <v>58106</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16007,27 +16007,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B123" t="n">
-        <v>58105</v>
+        <v>58379</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16138,7 +16138,7 @@
         <v>129344006</v>
       </c>
       <c r="B124" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>129344132</v>
       </c>
       <c r="B125" t="n">
-        <v>57729</v>
+        <v>57730</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>129681811</v>
       </c>
       <c r="B126" t="n">
-        <v>56709</v>
+        <v>56710</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B122" t="n">
-        <v>58106</v>
+        <v>58379</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16007,27 +16007,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B123" t="n">
-        <v>58379</v>
+        <v>58106</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -15879,27 +15879,27 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129344266</v>
+        <v>129344316</v>
       </c>
       <c r="B122" t="n">
-        <v>58379</v>
+        <v>58106</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -16007,27 +16007,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129344316</v>
+        <v>129344266</v>
       </c>
       <c r="B123" t="n">
-        <v>58106</v>
+        <v>58379</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129544884</v>
       </c>
       <c r="B4" t="n">
-        <v>57594</v>
+        <v>57595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>129599492</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>129544884</v>
       </c>
       <c r="B4" t="n">
-        <v>57595</v>
+        <v>57598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>129599492</v>
       </c>
       <c r="B5" t="n">
-        <v>57731</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>129681811</v>
       </c>
       <c r="B126" t="n">
-        <v>56710</v>
+        <v>56713</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -12998,7 +12998,7 @@
         <v>126682650</v>
       </c>
       <c r="B98" t="n">
-        <v>57547</v>
+        <v>57543</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127081558</v>
+        <v>127151841</v>
       </c>
       <c r="B99" t="n">
         <v>56864</v>
@@ -13182,17 +13182,17 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>561045</v>
+        <v>561051</v>
       </c>
       <c r="R99" t="n">
-        <v>6627604</v>
+        <v>6627608</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13216,27 +13216,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Plockade frön längs vägkanten och gick sen V, in i skogen mot Murmossen.</t>
+          <t>Plockade något ätbart från växterna på vägkanten</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13259,14 +13259,18 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY99" t="inlineStr"/>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127151841</v>
+        <v>127081558</v>
       </c>
       <c r="B100" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13318,17 +13322,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>561051</v>
+        <v>561045</v>
       </c>
       <c r="R100" t="n">
-        <v>6627608</v>
+        <v>6627604</v>
       </c>
       <c r="S100" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13352,27 +13356,27 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Plockade något ätbart från växterna på vägkanten</t>
+          <t>Plockade frön längs vägkanten och gick sen V, in i skogen mot Murmossen.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13395,11 +13399,7 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16505,7 +16505,7 @@
         <v>130347868</v>
       </c>
       <c r="B127" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16505,7 +16505,7 @@
         <v>130347868</v>
       </c>
       <c r="B127" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16505,7 +16505,7 @@
         <v>130347868</v>
       </c>
       <c r="B127" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16505,7 +16505,7 @@
         <v>130347868</v>
       </c>
       <c r="B127" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AY128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16637,6 +16637,146 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>130828940</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57053</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skogsmursvägen, Ramnäs sn, Vstm , Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>561050</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6627773</v>
+      </c>
+      <c r="S128" t="n">
+        <v>30</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Gick på grusvägen, skrämdes och flög upp i en tall i skogen mot Salsmossen</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AY131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16777,6 +16777,399 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>131300609</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57742</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Salsmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>561193</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6627694</v>
+      </c>
+      <c r="S129" t="n">
+        <v>50</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Det typiska skällande lätet (varningslätet/revirlätet).</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>131300006</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Salsmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>561193</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6627694</v>
+      </c>
+      <c r="S130" t="n">
+        <v>50</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Flyktläte</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>131301237</v>
+      </c>
+      <c r="B131" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Salsmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>561193</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6627694</v>
+      </c>
+      <c r="S131" t="n">
+        <v>50</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17044,7 +17044,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131301237</v>
+        <v>131315574</v>
       </c>
       <c r="B131" t="n">
         <v>58043</v>
@@ -17125,22 +17125,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16779,10 +16779,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131300609</v>
+        <v>131315574</v>
       </c>
       <c r="B129" t="n">
-        <v>57742</v>
+        <v>58043</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16790,21 +16790,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100137</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -16860,27 +16860,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Det typiska skällande lätet (varningslätet/revirlätet).</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16891,6 +16886,11 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
@@ -16907,10 +16907,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131300006</v>
+        <v>131300609</v>
       </c>
       <c r="B130" t="n">
-        <v>57881</v>
+        <v>57742</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16918,21 +16918,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>100137</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -17003,12 +17003,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Flyktläte</t>
+          <t>Det typiska skällande lätet (varningslätet/revirlätet).</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -17019,11 +17019,6 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -17033,21 +17028,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Via Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>131315574</v>
+        <v>131303238</v>
       </c>
       <c r="B131" t="n">
-        <v>58043</v>
+        <v>57881</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17055,21 +17046,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -17125,22 +17116,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -17165,7 +17156,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Via Pia Hagfors</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16642,7 +16642,7 @@
         <v>130828940</v>
       </c>
       <c r="B128" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>131315574</v>
       </c>
       <c r="B129" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>131300609</v>
       </c>
       <c r="B130" t="n">
-        <v>57742</v>
+        <v>57744</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>131303238</v>
       </c>
       <c r="B131" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16642,7 +16642,7 @@
         <v>130828940</v>
       </c>
       <c r="B128" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>131315574</v>
       </c>
       <c r="B129" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16907,10 +16907,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>131300609</v>
+        <v>131315434</v>
       </c>
       <c r="B130" t="n">
-        <v>57744</v>
+        <v>57745</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16988,27 +16988,27 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Det typiska skällande lätet (varningslätet/revirlätet).</t>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -17019,6 +17019,11 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -17028,7 +17033,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Via Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -17038,7 +17043,7 @@
         <v>131303238</v>
       </c>
       <c r="B131" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16782,7 +16782,7 @@
         <v>131315574</v>
       </c>
       <c r="B129" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>131315434</v>
       </c>
       <c r="B130" t="n">
-        <v>57745</v>
+        <v>57746</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>131303238</v>
       </c>
       <c r="B131" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17166,6 +17166,262 @@
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131440928</v>
+      </c>
+      <c r="B132" t="n">
+        <v>57729</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Murmosseskogen, Rmnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>561033</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6627718</v>
+      </c>
+      <c r="S132" t="n">
+        <v>50</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131437958</v>
+      </c>
+      <c r="B133" t="n">
+        <v>57746</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Murmosseskogen, Rmnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>561033</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6627718</v>
+      </c>
+      <c r="S133" t="n">
+        <v>50</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Avstånd uppskattningsvis &lt;100 meter fråb ljudboxen</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Via Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17168,7 +17168,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131440928</v>
+        <v>131499972</v>
       </c>
       <c r="B132" t="n">
         <v>57729</v>
@@ -17249,22 +17249,27 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>05:35</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Hördes på längre avstånd från inspelaren.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17284,7 +17289,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Via Pia Hagfors</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16782,7 +16782,7 @@
         <v>131315574</v>
       </c>
       <c r="B129" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>131315434</v>
       </c>
       <c r="B130" t="n">
-        <v>57746</v>
+        <v>57749</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>131303238</v>
       </c>
       <c r="B131" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17168,32 +17168,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131499972</v>
+        <v>131437958</v>
       </c>
       <c r="B132" t="n">
-        <v>57729</v>
+        <v>57749</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>102621</v>
+        <v>100137</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -17205,7 +17205,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -17249,27 +17249,27 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Hördes på längre avstånd från inspelaren.</t>
+          <t>Avstånd uppskattningsvis &lt;100 meter fråb ljudboxen</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17280,6 +17280,11 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -17296,32 +17301,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131437958</v>
+        <v>131440928</v>
       </c>
       <c r="B133" t="n">
-        <v>57746</v>
+        <v>57732</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100137</v>
+        <v>102621</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -17333,7 +17338,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -17377,27 +17382,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:35</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>05:15</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Avstånd uppskattningsvis &lt;100 meter fråb ljudboxen</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17408,11 +17408,6 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -17422,7 +17417,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Via Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -16782,7 +16782,7 @@
         <v>131315574</v>
       </c>
       <c r="B129" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>131315434</v>
       </c>
       <c r="B130" t="n">
-        <v>57749</v>
+        <v>57750</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>131303238</v>
       </c>
       <c r="B131" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -17168,32 +17168,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131437958</v>
+        <v>131440928</v>
       </c>
       <c r="B132" t="n">
-        <v>57749</v>
+        <v>57733</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100137</v>
+        <v>102621</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -17205,7 +17205,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -17249,27 +17249,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:35</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>05:15</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Avstånd uppskattningsvis &lt;100 meter fråb ljudboxen</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17280,11 +17275,6 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
@@ -17294,39 +17284,39 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Via Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>131440928</v>
+        <v>131437958</v>
       </c>
       <c r="B133" t="n">
-        <v>57732</v>
+        <v>57750</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>102621</v>
+        <v>100137</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -17338,7 +17328,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -17382,22 +17372,27 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>05:35</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Avstånd uppskattningsvis &lt;100 meter fråb ljudboxen</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17408,6 +17403,11 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Via Pia Hagfors</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17549,7 +17549,7 @@
         <v>131970341</v>
       </c>
       <c r="B135" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17827,6 +17827,127 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>132468205</v>
+      </c>
+      <c r="B137" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>561088</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6627651</v>
+      </c>
+      <c r="S137" t="n">
+        <v>20</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6858,7 +6858,7 @@
         <v>118810274</v>
       </c>
       <c r="B50" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>118849870</v>
       </c>
       <c r="B51" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>119733582</v>
       </c>
       <c r="B66" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>126682650</v>
       </c>
       <c r="B98" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>127945591</v>
       </c>
       <c r="B105" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>126075875</v>
       </c>
       <c r="B134" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>131970341</v>
       </c>
       <c r="B135" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>132074707</v>
       </c>
       <c r="B136" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>132468205</v>
       </c>
       <c r="B137" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17947,6 +17947,375 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>132660822</v>
+      </c>
+      <c r="B138" t="n">
+        <v>99106</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>560999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6627568</v>
+      </c>
+      <c r="S138" t="n">
+        <v>2</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>132660299</v>
+      </c>
+      <c r="B139" t="n">
+        <v>58493</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>561059</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6627663</v>
+      </c>
+      <c r="S139" t="n">
+        <v>25</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>132663002</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>561067</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6627834</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17829,57 +17829,62 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132468205</v>
+        <v>132660822</v>
       </c>
       <c r="B137" t="n">
-        <v>58110</v>
+        <v>99106</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>561088</v>
+        <v>560999</v>
       </c>
       <c r="R137" t="n">
-        <v>6627651</v>
+        <v>6627568</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17903,22 +17908,27 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17950,62 +17960,57 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132660822</v>
+        <v>132660299</v>
       </c>
       <c r="B138" t="n">
-        <v>99106</v>
+        <v>58493</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>560999</v>
+        <v>561059</v>
       </c>
       <c r="R138" t="n">
-        <v>6627568</v>
+        <v>6627663</v>
       </c>
       <c r="S138" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -18034,7 +18039,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -18044,12 +18049,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -18081,10 +18081,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132660299</v>
+        <v>132663002</v>
       </c>
       <c r="B139" t="n">
-        <v>58493</v>
+        <v>8455</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18092,46 +18092,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>102990</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>561059</v>
+        <v>561067</v>
       </c>
       <c r="R139" t="n">
-        <v>6627663</v>
+        <v>6627834</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -18160,7 +18156,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -18170,7 +18166,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18184,7 +18180,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -18202,53 +18198,57 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132663002</v>
+        <v>132468205</v>
       </c>
       <c r="B140" t="n">
-        <v>8455</v>
+        <v>58110</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>561067</v>
+        <v>561088</v>
       </c>
       <c r="R140" t="n">
-        <v>6627834</v>
+        <v>6627651</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -18272,22 +18272,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -6858,7 +6858,7 @@
         <v>118810274</v>
       </c>
       <c r="B50" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>118849870</v>
       </c>
       <c r="B51" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>119733582</v>
       </c>
       <c r="B66" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>126682650</v>
       </c>
       <c r="B98" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>127945591</v>
       </c>
       <c r="B105" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>126075875</v>
       </c>
       <c r="B134" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>131970341</v>
       </c>
       <c r="B135" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>132074707</v>
       </c>
       <c r="B136" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>132660822</v>
       </c>
       <c r="B137" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>132660299</v>
       </c>
       <c r="B138" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>132468205</v>
       </c>
       <c r="B140" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17832,7 +17832,7 @@
         <v>132660822</v>
       </c>
       <c r="B137" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17832,7 +17832,7 @@
         <v>132660822</v>
       </c>
       <c r="B137" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17960,10 +17960,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132660299</v>
+        <v>132663002</v>
       </c>
       <c r="B138" t="n">
-        <v>58497</v>
+        <v>8455</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17971,46 +17971,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>102990</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>561059</v>
+        <v>561067</v>
       </c>
       <c r="R138" t="n">
-        <v>6627663</v>
+        <v>6627834</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -18039,7 +18035,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -18049,7 +18045,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -18063,7 +18059,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -18081,53 +18077,57 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132663002</v>
+        <v>132468205</v>
       </c>
       <c r="B139" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>561067</v>
+        <v>561088</v>
       </c>
       <c r="R139" t="n">
-        <v>6627834</v>
+        <v>6627651</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -18151,22 +18151,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18198,32 +18198,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132468205</v>
+        <v>132660299</v>
       </c>
       <c r="B140" t="n">
-        <v>58114</v>
+        <v>58497</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -18238,17 +18238,17 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>561088</v>
+        <v>561059</v>
       </c>
       <c r="R140" t="n">
-        <v>6627651</v>
+        <v>6627663</v>
       </c>
       <c r="S140" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -18272,22 +18272,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17687,7 +17687,7 @@
         <v>132074707</v>
       </c>
       <c r="B136" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>132660822</v>
       </c>
       <c r="B137" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>132468205</v>
       </c>
       <c r="B139" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>132660299</v>
       </c>
       <c r="B140" t="n">
-        <v>58497</v>
+        <v>58498</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -17968,7 +17968,7 @@
         <v>132660822</v>
       </c>
       <c r="B138" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -18455,10 +18455,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133377787</v>
+        <v>133436635</v>
       </c>
       <c r="B142" t="n">
-        <v>57148</v>
+        <v>57950</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18466,24 +18466,28 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>102613</v>
+        <v>100110</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
@@ -18532,27 +18536,27 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Hörs på avstånd från Murmossen</t>
+          <t>Hörs tydligt på ljudboxen kl 19:25 och 19:43</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -18566,7 +18570,7 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>Myr</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -18584,10 +18588,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133436635</v>
+        <v>133377787</v>
       </c>
       <c r="B143" t="n">
-        <v>57950</v>
+        <v>57148</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18595,28 +18599,24 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100110</v>
+        <v>102613</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
@@ -18665,27 +18665,27 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Hörs tydligt på ljudboxen kl 19:25 och 19:43</t>
+          <t>Hörs på avstånd från Murmossen</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Myr</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -18720,7 +18720,7 @@
         <v>133764984</v>
       </c>
       <c r="B144" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>134161495</v>
       </c>
       <c r="B147" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY212"/>
+  <dimension ref="A1:AY216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24431,32 +24431,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>116192832</v>
+        <v>135147368</v>
       </c>
       <c r="B192" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -24466,27 +24466,27 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>561001</v>
+        <v>561051</v>
       </c>
       <c r="R192" t="n">
-        <v>6627609</v>
+        <v>6627607</v>
       </c>
       <c r="S192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24510,22 +24510,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -24536,11 +24536,6 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
@@ -24557,64 +24552,57 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>116196922</v>
+        <v>135147426</v>
       </c>
       <c r="B193" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>561103</v>
+        <v>561010</v>
       </c>
       <c r="R193" t="n">
-        <v>6627492</v>
+        <v>6627744</v>
       </c>
       <c r="S193" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -24638,22 +24626,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -24662,7 +24650,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -24686,68 +24673,62 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>116377628</v>
+        <v>135147597</v>
       </c>
       <c r="B194" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>560998</v>
+        <v>561003</v>
       </c>
       <c r="R194" t="n">
-        <v>6627569</v>
+        <v>6627860</v>
       </c>
       <c r="S194" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -24771,22 +24752,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -24795,13 +24776,12 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
@@ -24819,37 +24799,37 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>123329692</v>
+        <v>135147621</v>
       </c>
       <c r="B195" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -24859,28 +24839,22 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>561099</v>
+        <v>561005</v>
       </c>
       <c r="R195" t="n">
-        <v>6627492</v>
+        <v>6627859</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -24904,12 +24878,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24918,18 +24902,12 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr"/>
@@ -24947,10 +24925,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>132660822</v>
+        <v>116192832</v>
       </c>
       <c r="B196" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -24977,12 +24955,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -24992,17 +24970,17 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>560999</v>
+        <v>561001</v>
       </c>
       <c r="R196" t="n">
-        <v>6627568</v>
+        <v>6627609</v>
       </c>
       <c r="S196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -25026,27 +25004,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25078,48 +25051,64 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>4221674</v>
+        <v>116196922</v>
       </c>
       <c r="B197" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>561035</v>
+        <v>561103</v>
       </c>
       <c r="R197" t="n">
-        <v>6627874</v>
+        <v>6627492</v>
       </c>
       <c r="S197" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -25143,12 +25132,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25157,71 +25156,92 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>Tallskog/moränmark</t>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>4225188</v>
+        <v>116377628</v>
       </c>
       <c r="B198" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>561108</v>
+        <v>560998</v>
       </c>
       <c r="R198" t="n">
-        <v>6627497</v>
+        <v>6627569</v>
       </c>
       <c r="S198" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25245,17 +25265,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>sparsam</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25264,60 +25289,73 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>99086346</v>
+        <v>123329692</v>
       </c>
       <c r="B199" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
@@ -25326,14 +25364,14 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>561003</v>
+        <v>561099</v>
       </c>
       <c r="R199" t="n">
-        <v>6627635</v>
+        <v>6627492</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -25360,12 +25398,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25377,6 +25415,16 @@
       <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
+        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
@@ -25393,56 +25441,62 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>104578243</v>
+        <v>132660822</v>
       </c>
       <c r="B200" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>560987</v>
+        <v>560999</v>
       </c>
       <c r="R200" t="n">
-        <v>6627629</v>
+        <v>6627568</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -25466,12 +25520,27 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25480,7 +25549,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -25504,7 +25572,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>116192263</v>
+        <v>4221674</v>
       </c>
       <c r="B201" t="n">
         <v>97983</v>
@@ -25532,29 +25600,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>560991</v>
+        <v>561035</v>
       </c>
       <c r="R201" t="n">
-        <v>6627626</v>
+        <v>6627874</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -25578,22 +25637,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25605,27 +25654,27 @@
       <c r="AG201" t="b">
         <v>0</v>
       </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>Tallskog/moränmark</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126413111</v>
+        <v>4225188</v>
       </c>
       <c r="B202" t="n">
         <v>97983</v>
@@ -25653,29 +25702,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>561017</v>
+        <v>561108</v>
       </c>
       <c r="R202" t="n">
-        <v>6627814</v>
+        <v>6627497</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -25699,22 +25739,17 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -25725,23 +25760,28 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126413356</v>
+        <v>99086346</v>
       </c>
       <c r="B203" t="n">
         <v>97983</v>
@@ -25769,29 +25809,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>561013</v>
+        <v>561003</v>
       </c>
       <c r="R203" t="n">
-        <v>6627677</v>
+        <v>6627635</v>
       </c>
       <c r="S203" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -25815,22 +25854,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -25839,13 +25868,9 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
@@ -25862,7 +25887,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126416592</v>
+        <v>104578243</v>
       </c>
       <c r="B204" t="n">
         <v>97983</v>
@@ -25890,29 +25915,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>561027</v>
+        <v>560987</v>
       </c>
       <c r="R204" t="n">
-        <v>6627858</v>
+        <v>6627629</v>
       </c>
       <c r="S204" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -25936,22 +25960,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>17:54</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>17:54</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -25960,8 +25974,14 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
@@ -25978,7 +25998,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128162622</v>
+        <v>116192263</v>
       </c>
       <c r="B205" t="n">
         <v>97983</v>
@@ -26008,7 +26028,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -26018,17 +26038,17 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>561012</v>
+        <v>560991</v>
       </c>
       <c r="R205" t="n">
-        <v>6627671</v>
+        <v>6627626</v>
       </c>
       <c r="S205" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -26052,22 +26072,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26099,10 +26119,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133764984</v>
+        <v>126413111</v>
       </c>
       <c r="B206" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -26129,7 +26149,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -26139,17 +26159,17 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>561227</v>
+        <v>561017</v>
       </c>
       <c r="R206" t="n">
-        <v>6627267</v>
+        <v>6627814</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26173,22 +26193,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26199,11 +26219,6 @@
       </c>
       <c r="AG206" t="b">
         <v>0</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
@@ -26220,10 +26235,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>112959278</v>
+        <v>126413356</v>
       </c>
       <c r="B207" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -26231,16 +26246,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -26248,28 +26263,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>561019</v>
+        <v>561013</v>
       </c>
       <c r="R207" t="n">
-        <v>6627490</v>
+        <v>6627677</v>
       </c>
       <c r="S207" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26293,12 +26309,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26307,9 +26333,13 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
@@ -26326,10 +26356,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>134063381</v>
+        <v>126416592</v>
       </c>
       <c r="B208" t="n">
-        <v>99472</v>
+        <v>97983</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -26337,16 +26367,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -26354,25 +26384,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>560964</v>
+        <v>561027</v>
       </c>
       <c r="R208" t="n">
-        <v>6627632</v>
+        <v>6627858</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -26396,22 +26430,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -26422,11 +26456,6 @@
       </c>
       <c r="AG208" t="b">
         <v>0</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
@@ -26443,10 +26472,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>5979250</v>
+        <v>128162622</v>
       </c>
       <c r="B209" t="n">
-        <v>99038</v>
+        <v>97983</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -26454,47 +26483,46 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>560984</v>
+        <v>561012</v>
       </c>
       <c r="R209" t="n">
-        <v>6627735</v>
+        <v>6627671</v>
       </c>
       <c r="S209" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -26518,12 +26546,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26535,30 +26573,30 @@
       <c r="AG209" t="b">
         <v>0</v>
       </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>5979251</v>
+        <v>133764984</v>
       </c>
       <c r="B210" t="n">
-        <v>99038</v>
+        <v>98060</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -26566,47 +26604,46 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>560967</v>
+        <v>561227</v>
       </c>
       <c r="R210" t="n">
-        <v>6627698</v>
+        <v>6627267</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -26630,12 +26667,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -26647,30 +26694,30 @@
       <c r="AG210" t="b">
         <v>0</v>
       </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>5979254</v>
+        <v>112959278</v>
       </c>
       <c r="B211" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -26678,44 +26725,42 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>560937</v>
+        <v>561019</v>
       </c>
       <c r="R211" t="n">
-        <v>6627972</v>
+        <v>6627490</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -26742,12 +26787,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -26756,33 +26801,29 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>5979255</v>
+        <v>134063381</v>
       </c>
       <c r="B212" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -26790,47 +26831,42 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>560943</v>
+        <v>560964</v>
       </c>
       <c r="R212" t="n">
-        <v>6627939</v>
+        <v>6627632</v>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -26854,12 +26890,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -26871,23 +26917,471 @@
       <c r="AG212" t="b">
         <v>0</v>
       </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>5979250</v>
+      </c>
+      <c r="B213" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>560984</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6627735</v>
+      </c>
+      <c r="S213" t="n">
+        <v>25</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
           <t>Sören Larsson</t>
         </is>
       </c>
-      <c r="AX212" t="inlineStr">
+      <c r="AX213" t="inlineStr">
         <is>
           <t>Sören Larsson</t>
         </is>
       </c>
-      <c r="AY212" t="inlineStr"/>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>5979251</v>
+      </c>
+      <c r="B214" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>560967</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6627698</v>
+      </c>
+      <c r="S214" t="n">
+        <v>25</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B215" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S215" t="n">
+        <v>25</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B216" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S216" t="n">
+        <v>25</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY216"/>
+  <dimension ref="A1:AY218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>Bäcknära barrskog</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -23652,7 +23652,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Bäcknära barrskog</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -23670,10 +23670,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134797963</v>
+        <v>135221795</v>
       </c>
       <c r="B186" t="n">
-        <v>56856</v>
+        <v>56833</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -23681,23 +23681,19 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>1</t>
@@ -23718,14 +23714,14 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>560991</v>
+        <v>561104</v>
       </c>
       <c r="R186" t="n">
-        <v>6627590</v>
+        <v>6627571</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -23752,27 +23748,27 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -23786,12 +23782,12 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>Bäcknära barrskog</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -23809,10 +23805,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>91949709</v>
+        <v>134797963</v>
       </c>
       <c r="B187" t="n">
-        <v>56522</v>
+        <v>56856</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -23820,21 +23816,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>206004</v>
+        <v>206002</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -23842,28 +23838,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>561067</v>
+        <v>560991</v>
       </c>
       <c r="R187" t="n">
-        <v>6627551</v>
+        <v>6627590</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -23890,27 +23887,27 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Sprang över Skogsmursvägen  helvit</t>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23921,6 +23918,16 @@
       </c>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
@@ -23937,32 +23944,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126415504</v>
+        <v>135221801</v>
       </c>
       <c r="B188" t="n">
-        <v>58817</v>
+        <v>56856</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>208249</v>
+        <v>206002</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -23970,28 +23977,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>561023</v>
+        <v>561104</v>
       </c>
       <c r="R188" t="n">
-        <v>6627575</v>
+        <v>6627571</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -24015,22 +24026,27 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24039,13 +24055,17 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -24063,32 +24083,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118334109</v>
+        <v>91949709</v>
       </c>
       <c r="B189" t="n">
-        <v>99035</v>
+        <v>56522</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -24098,22 +24118,29 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>561057</v>
+        <v>561067</v>
       </c>
       <c r="R189" t="n">
-        <v>6627592</v>
+        <v>6627551</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -24137,22 +24164,27 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Sprang över Skogsmursvägen  helvit</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24163,11 +24195,6 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
@@ -24184,10 +24211,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126416641</v>
+        <v>126415504</v>
       </c>
       <c r="B190" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -24195,21 +24222,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -24217,24 +24244,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>561018</v>
+        <v>561023</v>
       </c>
       <c r="R190" t="n">
-        <v>6627875</v>
+        <v>6627575</v>
       </c>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -24263,7 +24294,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24273,7 +24304,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24282,12 +24313,13 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr"/>
@@ -24305,10 +24337,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135071078</v>
+        <v>118334109</v>
       </c>
       <c r="B191" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -24335,12 +24367,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -24350,17 +24377,17 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>561117</v>
+        <v>561057</v>
       </c>
       <c r="R191" t="n">
-        <v>6627574</v>
+        <v>6627592</v>
       </c>
       <c r="S191" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -24384,22 +24411,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24413,7 +24440,7 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr"/>
@@ -24431,10 +24458,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135147368</v>
+        <v>126416641</v>
       </c>
       <c r="B192" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -24464,11 +24491,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K192" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -24476,17 +24498,17 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>561051</v>
+        <v>561018</v>
       </c>
       <c r="R192" t="n">
-        <v>6627607</v>
+        <v>6627875</v>
       </c>
       <c r="S192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24510,22 +24532,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -24536,6 +24558,11 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
@@ -24552,7 +24579,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>135147426</v>
+        <v>135071078</v>
       </c>
       <c r="B193" t="n">
         <v>99112</v>
@@ -24582,7 +24609,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -24592,17 +24624,17 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>561010</v>
+        <v>561117</v>
       </c>
       <c r="R193" t="n">
-        <v>6627744</v>
+        <v>6627574</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -24626,22 +24658,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -24655,7 +24687,7 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -24673,7 +24705,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135147597</v>
+        <v>135147368</v>
       </c>
       <c r="B194" t="n">
         <v>99112</v>
@@ -24703,7 +24735,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -24722,13 +24754,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>561003</v>
+        <v>561051</v>
       </c>
       <c r="R194" t="n">
-        <v>6627860</v>
+        <v>6627607</v>
       </c>
       <c r="S194" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -24757,7 +24789,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -24767,7 +24799,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -24778,11 +24810,6 @@
       </c>
       <c r="AG194" t="b">
         <v>0</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
@@ -24799,7 +24826,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135147621</v>
+        <v>135147426</v>
       </c>
       <c r="B195" t="n">
         <v>99112</v>
@@ -24829,12 +24856,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -24844,17 +24866,17 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>561005</v>
+        <v>561010</v>
       </c>
       <c r="R195" t="n">
-        <v>6627859</v>
+        <v>6627744</v>
       </c>
       <c r="S195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -24883,7 +24905,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -24893,7 +24915,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24925,62 +24947,62 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>116192832</v>
+        <v>135147597</v>
       </c>
       <c r="B196" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>561001</v>
+        <v>561003</v>
       </c>
       <c r="R196" t="n">
-        <v>6627609</v>
+        <v>6627860</v>
       </c>
       <c r="S196" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -25004,22 +25026,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25033,7 +25055,7 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -25051,32 +25073,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>116196922</v>
+        <v>135147621</v>
       </c>
       <c r="B197" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -25086,29 +25108,27 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>561103</v>
+        <v>561005</v>
       </c>
       <c r="R197" t="n">
-        <v>6627492</v>
+        <v>6627859</v>
       </c>
       <c r="S197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -25132,22 +25152,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25156,7 +25176,6 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -25180,7 +25199,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>116377628</v>
+        <v>116192832</v>
       </c>
       <c r="B198" t="n">
         <v>99118</v>
@@ -25223,22 +25242,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr"/>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>560998</v>
+        <v>561001</v>
       </c>
       <c r="R198" t="n">
-        <v>6627569</v>
+        <v>6627609</v>
       </c>
       <c r="S198" t="n">
         <v>1</v>
@@ -25265,22 +25278,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25289,7 +25302,6 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
@@ -25313,7 +25325,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>123329692</v>
+        <v>116196922</v>
       </c>
       <c r="B199" t="n">
         <v>99118</v>
@@ -25343,12 +25355,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -25357,24 +25369,20 @@
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>561099</v>
+        <v>561103</v>
       </c>
       <c r="R199" t="n">
         <v>6627492</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -25398,12 +25406,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25419,11 +25437,6 @@
       <c r="AH199" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr"/>
@@ -25441,10 +25454,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>132660822</v>
+        <v>116377628</v>
       </c>
       <c r="B200" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -25471,12 +25484,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -25484,19 +25497,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>560999</v>
+        <v>560998</v>
       </c>
       <c r="R200" t="n">
-        <v>6627568</v>
+        <v>6627569</v>
       </c>
       <c r="S200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -25520,27 +25539,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25549,6 +25563,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -25572,48 +25587,68 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>4221674</v>
+        <v>123329692</v>
       </c>
       <c r="B201" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>561035</v>
+        <v>561099</v>
       </c>
       <c r="R201" t="n">
-        <v>6627874</v>
+        <v>6627492</v>
       </c>
       <c r="S201" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -25637,12 +25672,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25651,71 +25686,91 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>Tallskog/moränmark</t>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>4225188</v>
+        <v>132660822</v>
       </c>
       <c r="B202" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>561108</v>
+        <v>560999</v>
       </c>
       <c r="R202" t="n">
-        <v>6627497</v>
+        <v>6627568</v>
       </c>
       <c r="S202" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -25739,17 +25794,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>sparsam</t>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -25761,27 +25826,27 @@
       <c r="AG202" t="b">
         <v>0</v>
       </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>99086346</v>
+        <v>4221674</v>
       </c>
       <c r="B203" t="n">
         <v>97983</v>
@@ -25810,27 +25875,19 @@
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>561003</v>
+        <v>561035</v>
       </c>
       <c r="R203" t="n">
-        <v>6627635</v>
+        <v>6627874</v>
       </c>
       <c r="S203" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -25854,12 +25911,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -25868,26 +25925,30 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>Tallskog/moränmark</t>
+        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>104578243</v>
+        <v>4225188</v>
       </c>
       <c r="B204" t="n">
         <v>97983</v>
@@ -25916,27 +25977,19 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>560987</v>
+        <v>561108</v>
       </c>
       <c r="R204" t="n">
-        <v>6627629</v>
+        <v>6627497</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -25960,12 +26013,17 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -25974,31 +26032,30 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>116192263</v>
+        <v>99086346</v>
       </c>
       <c r="B205" t="n">
         <v>97983</v>
@@ -26026,26 +26083,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>560991</v>
+        <v>561003</v>
       </c>
       <c r="R205" t="n">
-        <v>6627626</v>
+        <v>6627635</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -26072,22 +26128,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26096,13 +26142,9 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
@@ -26119,7 +26161,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126413111</v>
+        <v>104578243</v>
       </c>
       <c r="B206" t="n">
         <v>97983</v>
@@ -26147,29 +26189,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>561017</v>
+        <v>560987</v>
       </c>
       <c r="R206" t="n">
-        <v>6627814</v>
+        <v>6627629</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26193,22 +26234,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26217,8 +26248,14 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
@@ -26235,7 +26272,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126413356</v>
+        <v>116192263</v>
       </c>
       <c r="B207" t="n">
         <v>97983</v>
@@ -26265,7 +26302,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -26275,17 +26312,17 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>561013</v>
+        <v>560991</v>
       </c>
       <c r="R207" t="n">
-        <v>6627677</v>
+        <v>6627626</v>
       </c>
       <c r="S207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26309,22 +26346,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26356,7 +26393,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126416592</v>
+        <v>126413111</v>
       </c>
       <c r="B208" t="n">
         <v>97983</v>
@@ -26386,7 +26423,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -26400,13 +26437,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>561027</v>
+        <v>561017</v>
       </c>
       <c r="R208" t="n">
-        <v>6627858</v>
+        <v>6627814</v>
       </c>
       <c r="S208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -26435,7 +26472,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -26445,7 +26482,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -26472,7 +26509,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128162622</v>
+        <v>126413356</v>
       </c>
       <c r="B209" t="n">
         <v>97983</v>
@@ -26516,10 +26553,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>561012</v>
+        <v>561013</v>
       </c>
       <c r="R209" t="n">
-        <v>6627671</v>
+        <v>6627677</v>
       </c>
       <c r="S209" t="n">
         <v>1</v>
@@ -26546,22 +26583,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26593,10 +26630,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133764984</v>
+        <v>126416592</v>
       </c>
       <c r="B210" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -26623,7 +26660,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -26633,17 +26670,17 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>561227</v>
+        <v>561027</v>
       </c>
       <c r="R210" t="n">
-        <v>6627267</v>
+        <v>6627858</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -26667,22 +26704,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -26693,11 +26730,6 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
@@ -26714,10 +26746,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>112959278</v>
+        <v>128162622</v>
       </c>
       <c r="B211" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -26725,16 +26757,16 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -26742,28 +26774,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561019</v>
+        <v>561012</v>
       </c>
       <c r="R211" t="n">
-        <v>6627490</v>
+        <v>6627671</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -26787,12 +26820,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -26801,9 +26844,13 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
@@ -26820,10 +26867,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>134063381</v>
+        <v>133764984</v>
       </c>
       <c r="B212" t="n">
-        <v>99472</v>
+        <v>98060</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -26831,16 +26878,16 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -26848,25 +26895,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>560964</v>
+        <v>561227</v>
       </c>
       <c r="R212" t="n">
-        <v>6627632</v>
+        <v>6627267</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -26890,22 +26941,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -26937,10 +26988,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>5979250</v>
+        <v>112959278</v>
       </c>
       <c r="B213" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -26948,44 +26999,42 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>560984</v>
+        <v>561019</v>
       </c>
       <c r="R213" t="n">
-        <v>6627735</v>
+        <v>6627490</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -27012,12 +27061,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -27026,33 +27075,29 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>5979251</v>
+        <v>134063381</v>
       </c>
       <c r="B214" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -27060,47 +27105,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>560967</v>
+        <v>560964</v>
       </c>
       <c r="R214" t="n">
-        <v>6627698</v>
+        <v>6627632</v>
       </c>
       <c r="S214" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -27124,12 +27164,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -27141,27 +27191,27 @@
       <c r="AG214" t="b">
         <v>0</v>
       </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>5979254</v>
+        <v>5979250</v>
       </c>
       <c r="B215" t="n">
         <v>99038</v>
@@ -27187,7 +27237,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -27206,10 +27256,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>560937</v>
+        <v>560984</v>
       </c>
       <c r="R215" t="n">
-        <v>6627972</v>
+        <v>6627735</v>
       </c>
       <c r="S215" t="n">
         <v>25</v>
@@ -27273,7 +27323,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>5979255</v>
+        <v>5979251</v>
       </c>
       <c r="B216" t="n">
         <v>99038</v>
@@ -27299,7 +27349,7 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -27318,10 +27368,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>560943</v>
+        <v>560967</v>
       </c>
       <c r="R216" t="n">
-        <v>6627939</v>
+        <v>6627698</v>
       </c>
       <c r="S216" t="n">
         <v>25</v>
@@ -27382,6 +27432,230 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B217" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S217" t="n">
+        <v>25</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B218" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S218" t="n">
+        <v>25</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY219"/>
+  <dimension ref="A1:AY221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23384,10 +23384,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>134847157</v>
+        <v>135407739</v>
       </c>
       <c r="B184" t="n">
-        <v>56854</v>
+        <v>56842</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -23395,36 +23395,36 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -23432,14 +23432,14 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>560991</v>
+        <v>561206</v>
       </c>
       <c r="R184" t="n">
-        <v>6627590</v>
+        <v>6627647</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -23466,27 +23466,27 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>03:16</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
+          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -23500,12 +23500,12 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -23523,33 +23523,37 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>134845434</v>
+        <v>134847157</v>
       </c>
       <c r="B185" t="n">
-        <v>56833</v>
+        <v>56854</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -23571,10 +23575,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>561038</v>
+        <v>560991</v>
       </c>
       <c r="R185" t="n">
-        <v>6627624</v>
+        <v>6627590</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -23606,22 +23610,22 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Minst 213 ekolokaliseringssekvenser och 32 feeding buzz registrerdes under natten. Arten använder området för födosök.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -23640,7 +23644,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>Sumpskogsomåde</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -23658,7 +23662,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>134797837</v>
+        <v>134845434</v>
       </c>
       <c r="B186" t="n">
         <v>56833</v>
@@ -23684,7 +23688,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -23694,7 +23698,11 @@
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N186" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -23706,10 +23714,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>560991</v>
+        <v>561038</v>
       </c>
       <c r="R186" t="n">
-        <v>6627590</v>
+        <v>6627624</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -23741,22 +23749,22 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Minst 213 ekolokaliseringssekvenser och 32 feeding buzz registrerdes under natten. Arten använder området för födosök.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -23775,7 +23783,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Sumpskogsomåde</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -23793,7 +23801,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>135221795</v>
+        <v>134797837</v>
       </c>
       <c r="B187" t="n">
         <v>56833</v>
@@ -23819,7 +23827,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -23829,7 +23837,11 @@
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N187" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -23837,14 +23849,14 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>561104</v>
+        <v>560991</v>
       </c>
       <c r="R187" t="n">
-        <v>6627571</v>
+        <v>6627590</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -23871,27 +23883,27 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23905,12 +23917,12 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -23928,10 +23940,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>134797963</v>
+        <v>135221795</v>
       </c>
       <c r="B188" t="n">
-        <v>56856</v>
+        <v>56833</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23939,23 +23951,19 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>1</t>
@@ -23968,7 +23976,11 @@
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N188" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -23976,14 +23988,14 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>560991</v>
+        <v>561104</v>
       </c>
       <c r="R188" t="n">
-        <v>6627590</v>
+        <v>6627571</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -24010,27 +24022,27 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24044,12 +24056,12 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -24067,10 +24079,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>135221801</v>
+        <v>135406665</v>
       </c>
       <c r="B189" t="n">
-        <v>56856</v>
+        <v>56833</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -24078,36 +24090,32 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N189" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -24119,10 +24127,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>561104</v>
+        <v>561206</v>
       </c>
       <c r="R189" t="n">
-        <v>6627571</v>
+        <v>6627647</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -24149,7 +24157,7 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
@@ -24159,17 +24167,17 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>03:16</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
+          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24188,7 +24196,7 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>
@@ -24206,10 +24214,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>91949709</v>
+        <v>134797963</v>
       </c>
       <c r="B190" t="n">
-        <v>56522</v>
+        <v>56856</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -24217,21 +24225,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>206004</v>
+        <v>206002</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -24239,28 +24247,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>561067</v>
+        <v>560991</v>
       </c>
       <c r="R190" t="n">
-        <v>6627551</v>
+        <v>6627590</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -24287,27 +24296,27 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Sprang över Skogsmursvägen  helvit</t>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24318,6 +24327,16 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
@@ -24334,32 +24353,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126415504</v>
+        <v>135221801</v>
       </c>
       <c r="B191" t="n">
-        <v>58817</v>
+        <v>56856</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>208249</v>
+        <v>206002</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -24367,28 +24386,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>561023</v>
+        <v>561104</v>
       </c>
       <c r="R191" t="n">
-        <v>6627575</v>
+        <v>6627571</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -24412,22 +24435,27 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24436,13 +24464,17 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr"/>
@@ -24460,32 +24492,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118334109</v>
+        <v>91949709</v>
       </c>
       <c r="B192" t="n">
-        <v>99035</v>
+        <v>56522</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -24495,22 +24527,29 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>561057</v>
+        <v>561067</v>
       </c>
       <c r="R192" t="n">
-        <v>6627592</v>
+        <v>6627551</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24534,22 +24573,27 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Sprang över Skogsmursvägen  helvit</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -24560,11 +24604,6 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
@@ -24581,10 +24620,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126416641</v>
+        <v>126415504</v>
       </c>
       <c r="B193" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -24592,21 +24631,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -24614,24 +24653,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>561018</v>
+        <v>561023</v>
       </c>
       <c r="R193" t="n">
-        <v>6627875</v>
+        <v>6627575</v>
       </c>
       <c r="S193" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -24660,7 +24703,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -24670,7 +24713,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -24679,12 +24722,13 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -24702,10 +24746,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135071078</v>
+        <v>118334109</v>
       </c>
       <c r="B194" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -24732,12 +24776,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -24747,17 +24786,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>561117</v>
+        <v>561057</v>
       </c>
       <c r="R194" t="n">
-        <v>6627574</v>
+        <v>6627592</v>
       </c>
       <c r="S194" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -24781,22 +24820,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -24810,7 +24849,7 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
@@ -24828,10 +24867,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135147368</v>
+        <v>126416641</v>
       </c>
       <c r="B195" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -24861,11 +24900,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K195" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -24873,17 +24907,17 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>561051</v>
+        <v>561018</v>
       </c>
       <c r="R195" t="n">
-        <v>6627607</v>
+        <v>6627875</v>
       </c>
       <c r="S195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -24907,22 +24941,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24933,6 +24967,11 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
@@ -24949,7 +24988,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135147426</v>
+        <v>135071078</v>
       </c>
       <c r="B196" t="n">
         <v>99112</v>
@@ -24979,7 +25018,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -24989,17 +25033,17 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>561010</v>
+        <v>561117</v>
       </c>
       <c r="R196" t="n">
-        <v>6627744</v>
+        <v>6627574</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -25023,22 +25067,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25052,7 +25096,7 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -25070,7 +25114,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>135147597</v>
+        <v>135147368</v>
       </c>
       <c r="B197" t="n">
         <v>99112</v>
@@ -25100,7 +25144,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -25119,13 +25163,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>561003</v>
+        <v>561051</v>
       </c>
       <c r="R197" t="n">
-        <v>6627860</v>
+        <v>6627607</v>
       </c>
       <c r="S197" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -25154,7 +25198,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25164,7 +25208,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25175,11 +25219,6 @@
       </c>
       <c r="AG197" t="b">
         <v>0</v>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
@@ -25196,7 +25235,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>135147621</v>
+        <v>135147426</v>
       </c>
       <c r="B198" t="n">
         <v>99112</v>
@@ -25226,12 +25265,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -25241,17 +25275,17 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>561005</v>
+        <v>561010</v>
       </c>
       <c r="R198" t="n">
-        <v>6627859</v>
+        <v>6627744</v>
       </c>
       <c r="S198" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25280,7 +25314,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -25290,7 +25324,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25322,62 +25356,62 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>116192832</v>
+        <v>135147597</v>
       </c>
       <c r="B199" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>561001</v>
+        <v>561003</v>
       </c>
       <c r="R199" t="n">
-        <v>6627609</v>
+        <v>6627860</v>
       </c>
       <c r="S199" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -25401,22 +25435,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25430,7 +25464,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr"/>
@@ -25448,32 +25482,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>116196922</v>
+        <v>135147621</v>
       </c>
       <c r="B200" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -25483,29 +25517,27 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>561103</v>
+        <v>561005</v>
       </c>
       <c r="R200" t="n">
-        <v>6627492</v>
+        <v>6627859</v>
       </c>
       <c r="S200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -25529,22 +25561,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25553,7 +25585,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -25577,7 +25608,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>116377628</v>
+        <v>116192832</v>
       </c>
       <c r="B201" t="n">
         <v>99118</v>
@@ -25620,22 +25651,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>560998</v>
+        <v>561001</v>
       </c>
       <c r="R201" t="n">
-        <v>6627569</v>
+        <v>6627609</v>
       </c>
       <c r="S201" t="n">
         <v>1</v>
@@ -25662,22 +25687,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25686,7 +25711,6 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -25710,7 +25734,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>123329692</v>
+        <v>116196922</v>
       </c>
       <c r="B202" t="n">
         <v>99118</v>
@@ -25740,12 +25764,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -25754,24 +25778,20 @@
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>561099</v>
+        <v>561103</v>
       </c>
       <c r="R202" t="n">
         <v>6627492</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -25795,12 +25815,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -25816,11 +25846,6 @@
       <c r="AH202" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr"/>
@@ -25838,10 +25863,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>132660822</v>
+        <v>116377628</v>
       </c>
       <c r="B203" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25868,12 +25893,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -25881,19 +25906,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>560999</v>
+        <v>560998</v>
       </c>
       <c r="R203" t="n">
-        <v>6627568</v>
+        <v>6627569</v>
       </c>
       <c r="S203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -25917,27 +25948,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -25946,6 +25972,7 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -25969,48 +25996,68 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>4221674</v>
+        <v>123329692</v>
       </c>
       <c r="B204" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>561035</v>
+        <v>561099</v>
       </c>
       <c r="R204" t="n">
-        <v>6627874</v>
+        <v>6627492</v>
       </c>
       <c r="S204" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -26034,12 +26081,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26048,71 +26095,91 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>Tallskog/moränmark</t>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>4225188</v>
+        <v>132660822</v>
       </c>
       <c r="B205" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>561108</v>
+        <v>560999</v>
       </c>
       <c r="R205" t="n">
-        <v>6627497</v>
+        <v>6627568</v>
       </c>
       <c r="S205" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -26136,17 +26203,27 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>sparsam</t>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26158,27 +26235,27 @@
       <c r="AG205" t="b">
         <v>0</v>
       </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>99086346</v>
+        <v>4221674</v>
       </c>
       <c r="B206" t="n">
         <v>97983</v>
@@ -26207,27 +26284,19 @@
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>561003</v>
+        <v>561035</v>
       </c>
       <c r="R206" t="n">
-        <v>6627635</v>
+        <v>6627874</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26251,12 +26320,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26265,26 +26334,30 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>Tallskog/moränmark</t>
+        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>104578243</v>
+        <v>4225188</v>
       </c>
       <c r="B207" t="n">
         <v>97983</v>
@@ -26313,27 +26386,19 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>560987</v>
+        <v>561108</v>
       </c>
       <c r="R207" t="n">
-        <v>6627629</v>
+        <v>6627497</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26357,12 +26422,17 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26371,31 +26441,30 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>116192263</v>
+        <v>99086346</v>
       </c>
       <c r="B208" t="n">
         <v>97983</v>
@@ -26423,26 +26492,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>560991</v>
+        <v>561003</v>
       </c>
       <c r="R208" t="n">
-        <v>6627626</v>
+        <v>6627635</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -26469,22 +26537,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -26493,13 +26551,9 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
@@ -26516,7 +26570,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126413111</v>
+        <v>104578243</v>
       </c>
       <c r="B209" t="n">
         <v>97983</v>
@@ -26544,29 +26598,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>561017</v>
+        <v>560987</v>
       </c>
       <c r="R209" t="n">
-        <v>6627814</v>
+        <v>6627629</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -26590,22 +26643,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26614,8 +26657,14 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
@@ -26632,7 +26681,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>126413356</v>
+        <v>116192263</v>
       </c>
       <c r="B210" t="n">
         <v>97983</v>
@@ -26662,7 +26711,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -26672,17 +26721,17 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>561013</v>
+        <v>560991</v>
       </c>
       <c r="R210" t="n">
-        <v>6627677</v>
+        <v>6627626</v>
       </c>
       <c r="S210" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -26706,22 +26755,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -26753,7 +26802,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126416592</v>
+        <v>126413111</v>
       </c>
       <c r="B211" t="n">
         <v>97983</v>
@@ -26783,7 +26832,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -26797,13 +26846,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561027</v>
+        <v>561017</v>
       </c>
       <c r="R211" t="n">
-        <v>6627858</v>
+        <v>6627814</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -26832,7 +26881,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -26842,7 +26891,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -26869,7 +26918,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128162622</v>
+        <v>126413356</v>
       </c>
       <c r="B212" t="n">
         <v>97983</v>
@@ -26913,10 +26962,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>561012</v>
+        <v>561013</v>
       </c>
       <c r="R212" t="n">
-        <v>6627671</v>
+        <v>6627677</v>
       </c>
       <c r="S212" t="n">
         <v>1</v>
@@ -26943,22 +26992,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -26990,10 +27039,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>133764984</v>
+        <v>126416592</v>
       </c>
       <c r="B213" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -27020,7 +27069,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -27030,17 +27079,17 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>561227</v>
+        <v>561027</v>
       </c>
       <c r="R213" t="n">
-        <v>6627267</v>
+        <v>6627858</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -27064,22 +27113,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -27090,11 +27139,6 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
@@ -27111,10 +27155,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>112959278</v>
+        <v>128162622</v>
       </c>
       <c r="B214" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -27122,16 +27166,16 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -27139,28 +27183,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>561019</v>
+        <v>561012</v>
       </c>
       <c r="R214" t="n">
-        <v>6627490</v>
+        <v>6627671</v>
       </c>
       <c r="S214" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -27184,12 +27229,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -27198,9 +27253,13 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
@@ -27217,10 +27276,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134063381</v>
+        <v>133764984</v>
       </c>
       <c r="B215" t="n">
-        <v>99472</v>
+        <v>98060</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -27228,16 +27287,16 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -27245,25 +27304,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>560964</v>
+        <v>561227</v>
       </c>
       <c r="R215" t="n">
-        <v>6627632</v>
+        <v>6627267</v>
       </c>
       <c r="S215" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -27287,22 +27350,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -27334,10 +27397,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>5979250</v>
+        <v>112959278</v>
       </c>
       <c r="B216" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -27345,44 +27408,42 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>560984</v>
+        <v>561019</v>
       </c>
       <c r="R216" t="n">
-        <v>6627735</v>
+        <v>6627490</v>
       </c>
       <c r="S216" t="n">
         <v>25</v>
@@ -27409,12 +27470,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -27423,33 +27484,29 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>5979251</v>
+        <v>134063381</v>
       </c>
       <c r="B217" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -27457,47 +27514,42 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>560967</v>
+        <v>560964</v>
       </c>
       <c r="R217" t="n">
-        <v>6627698</v>
+        <v>6627632</v>
       </c>
       <c r="S217" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -27521,12 +27573,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -27538,27 +27600,27 @@
       <c r="AG217" t="b">
         <v>0</v>
       </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>5979254</v>
+        <v>5979250</v>
       </c>
       <c r="B218" t="n">
         <v>99038</v>
@@ -27584,7 +27646,7 @@
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -27603,10 +27665,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>560937</v>
+        <v>560984</v>
       </c>
       <c r="R218" t="n">
-        <v>6627972</v>
+        <v>6627735</v>
       </c>
       <c r="S218" t="n">
         <v>25</v>
@@ -27670,7 +27732,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>5979255</v>
+        <v>5979251</v>
       </c>
       <c r="B219" t="n">
         <v>99038</v>
@@ -27696,7 +27758,7 @@
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -27715,10 +27777,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>560943</v>
+        <v>560967</v>
       </c>
       <c r="R219" t="n">
-        <v>6627939</v>
+        <v>6627698</v>
       </c>
       <c r="S219" t="n">
         <v>25</v>
@@ -27779,6 +27841,230 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B220" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S220" t="n">
+        <v>25</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B221" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S221" t="n">
+        <v>25</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ224"/>
+  <dimension ref="A1:AZ225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26011,32 +26011,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126415504</v>
+        <v>135589893</v>
       </c>
       <c r="B196" t="n">
-        <v>58817</v>
+        <v>56706</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -26044,28 +26044,39 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>561023</v>
+        <v>561272</v>
       </c>
       <c r="R196" t="n">
-        <v>6627575</v>
+        <v>6627729</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26089,22 +26100,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26113,13 +26124,17 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -26136,16 +26151,16 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126415504</t>
+          <t>https://artportalen.se/Sighting/135589893</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118334109</v>
+        <v>126415504</v>
       </c>
       <c r="B197" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -26153,21 +26168,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -26175,21 +26190,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>561057</v>
+        <v>561023</v>
       </c>
       <c r="R197" t="n">
-        <v>6627592</v>
+        <v>6627575</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -26216,22 +26235,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -26240,12 +26259,13 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr"/>
@@ -26262,13 +26282,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118334109</t>
+          <t>https://artportalen.se/Sighting/126415504</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126416641</v>
+        <v>118334109</v>
       </c>
       <c r="B198" t="n">
         <v>99035</v>
@@ -26308,17 +26328,17 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>561018</v>
+        <v>561057</v>
       </c>
       <c r="R198" t="n">
-        <v>6627875</v>
+        <v>6627592</v>
       </c>
       <c r="S198" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -26342,22 +26362,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -26388,16 +26408,16 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416641</t>
+          <t>https://artportalen.se/Sighting/118334109</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135071078</v>
+        <v>126416641</v>
       </c>
       <c r="B199" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -26424,12 +26444,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -26439,17 +26454,17 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>561117</v>
+        <v>561018</v>
       </c>
       <c r="R199" t="n">
-        <v>6627574</v>
+        <v>6627875</v>
       </c>
       <c r="S199" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -26473,22 +26488,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -26502,7 +26517,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr"/>
@@ -26519,13 +26534,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071078</t>
+          <t>https://artportalen.se/Sighting/126416641</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135147368</v>
+        <v>135071078</v>
       </c>
       <c r="B200" t="n">
         <v>99112</v>
@@ -26555,7 +26570,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -26574,13 +26589,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>561051</v>
+        <v>561117</v>
       </c>
       <c r="R200" t="n">
-        <v>6627607</v>
+        <v>6627574</v>
       </c>
       <c r="S200" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -26604,22 +26619,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -26630,6 +26645,11 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -26645,13 +26665,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147368</t>
+          <t>https://artportalen.se/Sighting/135071078</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135147426</v>
+        <v>135147368</v>
       </c>
       <c r="B201" t="n">
         <v>99112</v>
@@ -26681,7 +26701,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -26691,17 +26716,17 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>561010</v>
+        <v>561051</v>
       </c>
       <c r="R201" t="n">
-        <v>6627744</v>
+        <v>6627607</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -26730,7 +26755,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -26740,7 +26765,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -26751,11 +26776,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -26771,13 +26791,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147426</t>
+          <t>https://artportalen.se/Sighting/135147368</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135147597</v>
+        <v>135147426</v>
       </c>
       <c r="B202" t="n">
         <v>99112</v>
@@ -26807,12 +26827,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -26822,17 +26837,17 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>561003</v>
+        <v>561010</v>
       </c>
       <c r="R202" t="n">
-        <v>6627860</v>
+        <v>6627744</v>
       </c>
       <c r="S202" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -26861,7 +26876,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26871,7 +26886,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26885,7 +26900,7 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr"/>
@@ -26902,13 +26917,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147597</t>
+          <t>https://artportalen.se/Sighting/135147426</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135147621</v>
+        <v>135147597</v>
       </c>
       <c r="B203" t="n">
         <v>99112</v>
@@ -26938,7 +26953,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -26957,13 +26972,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>561005</v>
+        <v>561003</v>
       </c>
       <c r="R203" t="n">
-        <v>6627859</v>
+        <v>6627860</v>
       </c>
       <c r="S203" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -26992,7 +27007,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -27002,7 +27017,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27016,7 +27031,7 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr"/>
@@ -27033,38 +27048,38 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147621</t>
+          <t>https://artportalen.se/Sighting/135147597</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>116192832</v>
+        <v>135147621</v>
       </c>
       <c r="B204" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -27074,27 +27089,27 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>561001</v>
+        <v>561005</v>
       </c>
       <c r="R204" t="n">
-        <v>6627609</v>
+        <v>6627859</v>
       </c>
       <c r="S204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27118,22 +27133,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27164,13 +27179,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192832</t>
+          <t>https://artportalen.se/Sighting/135147621</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>116196922</v>
+        <v>116192832</v>
       </c>
       <c r="B205" t="n">
         <v>99118</v>
@@ -27213,18 +27228,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>561103</v>
+        <v>561001</v>
       </c>
       <c r="R205" t="n">
-        <v>6627492</v>
+        <v>6627609</v>
       </c>
       <c r="S205" t="n">
         <v>1</v>
@@ -27256,7 +27269,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -27266,7 +27279,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27275,7 +27288,6 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -27298,13 +27310,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116196922</t>
+          <t>https://artportalen.se/Sighting/116192832</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>116377628</v>
+        <v>116196922</v>
       </c>
       <c r="B206" t="n">
         <v>99118</v>
@@ -27348,21 +27360,17 @@
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>560998</v>
+        <v>561103</v>
       </c>
       <c r="R206" t="n">
-        <v>6627569</v>
+        <v>6627492</v>
       </c>
       <c r="S206" t="n">
         <v>1</v>
@@ -27389,22 +27397,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -27436,13 +27444,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116377628</t>
+          <t>https://artportalen.se/Sighting/116196922</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>123329692</v>
+        <v>116377628</v>
       </c>
       <c r="B207" t="n">
         <v>99118</v>
@@ -27472,12 +27480,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -27493,17 +27501,17 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>561099</v>
+        <v>560998</v>
       </c>
       <c r="R207" t="n">
-        <v>6627492</v>
+        <v>6627569</v>
       </c>
       <c r="S207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -27527,12 +27535,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -27550,11 +27568,6 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
-        </is>
-      </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
@@ -27569,16 +27582,16 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123329692</t>
+          <t>https://artportalen.se/Sighting/116377628</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>132660822</v>
+        <v>123329692</v>
       </c>
       <c r="B208" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27605,7 +27618,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -27618,19 +27631,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>560999</v>
+        <v>561099</v>
       </c>
       <c r="R208" t="n">
-        <v>6627568</v>
+        <v>6627492</v>
       </c>
       <c r="S208" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -27654,27 +27673,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -27683,12 +27687,18 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr"/>
@@ -27705,54 +27715,68 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132660822</t>
+          <t>https://artportalen.se/Sighting/123329692</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>4221674</v>
+        <v>132660822</v>
       </c>
       <c r="B209" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>561035</v>
+        <v>560999</v>
       </c>
       <c r="R209" t="n">
-        <v>6627874</v>
+        <v>6627568</v>
       </c>
       <c r="S209" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -27776,12 +27800,27 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27793,32 +27832,32 @@
       <c r="AG209" t="b">
         <v>0</v>
       </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>Tallskog/moränmark</t>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4221674</t>
+          <t>https://artportalen.se/Sighting/132660822</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>4225188</v>
+        <v>4221674</v>
       </c>
       <c r="B210" t="n">
         <v>97983</v>
@@ -27849,17 +27888,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>561108</v>
+        <v>561035</v>
       </c>
       <c r="R210" t="n">
-        <v>6627497</v>
+        <v>6627874</v>
       </c>
       <c r="S210" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27883,17 +27922,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>sparsam</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27907,30 +27941,30 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Tallskog/moränmark</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4225188</t>
+          <t>https://artportalen.se/Sighting/4221674</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>99086346</v>
+        <v>4225188</v>
       </c>
       <c r="B211" t="n">
         <v>97983</v>
@@ -27959,27 +27993,19 @@
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561003</v>
+        <v>561108</v>
       </c>
       <c r="R211" t="n">
-        <v>6627635</v>
+        <v>6627497</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28003,12 +28029,17 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28017,31 +28048,35 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
+        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99086346</t>
+          <t>https://artportalen.se/Sighting/4225188</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>104578243</v>
+        <v>99086346</v>
       </c>
       <c r="B212" t="n">
         <v>97983</v>
@@ -28080,17 +28115,17 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>560987</v>
+        <v>561003</v>
       </c>
       <c r="R212" t="n">
-        <v>6627629</v>
+        <v>6627635</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28114,12 +28149,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28132,11 +28167,6 @@
       <c r="AG212" t="b">
         <v>0</v>
       </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
@@ -28151,13 +28181,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104578243</t>
+          <t>https://artportalen.se/Sighting/99086346</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>116192263</v>
+        <v>104578243</v>
       </c>
       <c r="B213" t="n">
         <v>97983</v>
@@ -28185,29 +28215,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>560991</v>
+        <v>560987</v>
       </c>
       <c r="R213" t="n">
-        <v>6627626</v>
+        <v>6627629</v>
       </c>
       <c r="S213" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28231,22 +28260,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28255,6 +28274,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -28277,13 +28297,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192263</t>
+          <t>https://artportalen.se/Sighting/104578243</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126413111</v>
+        <v>116192263</v>
       </c>
       <c r="B214" t="n">
         <v>97983</v>
@@ -28313,7 +28333,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -28323,14 +28343,14 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>561017</v>
+        <v>560991</v>
       </c>
       <c r="R214" t="n">
-        <v>6627814</v>
+        <v>6627626</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -28357,22 +28377,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -28383,6 +28403,11 @@
       </c>
       <c r="AG214" t="b">
         <v>0</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
@@ -28398,13 +28423,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413111</t>
+          <t>https://artportalen.se/Sighting/116192263</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126413356</v>
+        <v>126413111</v>
       </c>
       <c r="B215" t="n">
         <v>97983</v>
@@ -28434,7 +28459,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -28444,17 +28469,17 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>561013</v>
+        <v>561017</v>
       </c>
       <c r="R215" t="n">
-        <v>6627677</v>
+        <v>6627814</v>
       </c>
       <c r="S215" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -28483,7 +28508,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -28493,7 +28518,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -28504,11 +28529,6 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -28524,13 +28544,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413356</t>
+          <t>https://artportalen.se/Sighting/126413111</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126416592</v>
+        <v>126413356</v>
       </c>
       <c r="B216" t="n">
         <v>97983</v>
@@ -28570,14 +28590,14 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>561027</v>
+        <v>561013</v>
       </c>
       <c r="R216" t="n">
-        <v>6627858</v>
+        <v>6627677</v>
       </c>
       <c r="S216" t="n">
         <v>1</v>
@@ -28609,7 +28629,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -28619,7 +28639,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28630,6 +28650,11 @@
       </c>
       <c r="AG216" t="b">
         <v>0</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
@@ -28645,13 +28670,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416592</t>
+          <t>https://artportalen.se/Sighting/126413356</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128162622</v>
+        <v>126416592</v>
       </c>
       <c r="B217" t="n">
         <v>97983</v>
@@ -28691,14 +28716,14 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>561012</v>
+        <v>561027</v>
       </c>
       <c r="R217" t="n">
-        <v>6627671</v>
+        <v>6627858</v>
       </c>
       <c r="S217" t="n">
         <v>1</v>
@@ -28725,22 +28750,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28751,11 +28776,6 @@
       </c>
       <c r="AG217" t="b">
         <v>0</v>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
@@ -28771,16 +28791,16 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162622</t>
+          <t>https://artportalen.se/Sighting/126416592</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133764984</v>
+        <v>128162622</v>
       </c>
       <c r="B218" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -28807,7 +28827,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -28817,17 +28837,17 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>561227</v>
+        <v>561012</v>
       </c>
       <c r="R218" t="n">
-        <v>6627267</v>
+        <v>6627671</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -28851,22 +28871,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -28897,16 +28917,16 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133764984</t>
+          <t>https://artportalen.se/Sighting/128162622</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>112959278</v>
+        <v>133764984</v>
       </c>
       <c r="B219" t="n">
-        <v>97986</v>
+        <v>98060</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -28914,16 +28934,16 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -28931,28 +28951,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>561019</v>
+        <v>561227</v>
       </c>
       <c r="R219" t="n">
-        <v>6627490</v>
+        <v>6627267</v>
       </c>
       <c r="S219" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -28976,12 +28997,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -28990,9 +29021,13 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
@@ -29008,16 +29043,16 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959278</t>
+          <t>https://artportalen.se/Sighting/133764984</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>134063381</v>
+        <v>112959278</v>
       </c>
       <c r="B220" t="n">
-        <v>99472</v>
+        <v>97986</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -29025,16 +29060,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>222812</v>
+        <v>221946</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -29043,24 +29078,27 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>560964</v>
+        <v>561019</v>
       </c>
       <c r="R220" t="n">
-        <v>6627632</v>
+        <v>6627490</v>
       </c>
       <c r="S220" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29084,22 +29122,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29108,13 +29136,9 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
@@ -29130,16 +29154,16 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134063381</t>
+          <t>https://artportalen.se/Sighting/112959278</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>5979250</v>
+        <v>134063381</v>
       </c>
       <c r="B221" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -29147,47 +29171,42 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>560984</v>
+        <v>560964</v>
       </c>
       <c r="R221" t="n">
-        <v>6627735</v>
+        <v>6627632</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29211,12 +29230,22 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29228,32 +29257,32 @@
       <c r="AG221" t="b">
         <v>0</v>
       </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979250</t>
+          <t>https://artportalen.se/Sighting/134063381</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>5979251</v>
+        <v>5979250</v>
       </c>
       <c r="B222" t="n">
         <v>99038</v>
@@ -29298,10 +29327,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>560967</v>
+        <v>560984</v>
       </c>
       <c r="R222" t="n">
-        <v>6627698</v>
+        <v>6627735</v>
       </c>
       <c r="S222" t="n">
         <v>25</v>
@@ -29364,13 +29393,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979251</t>
+          <t>https://artportalen.se/Sighting/5979250</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>5979254</v>
+        <v>5979251</v>
       </c>
       <c r="B223" t="n">
         <v>99038</v>
@@ -29396,7 +29425,7 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -29415,10 +29444,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>560937</v>
+        <v>560967</v>
       </c>
       <c r="R223" t="n">
-        <v>6627972</v>
+        <v>6627698</v>
       </c>
       <c r="S223" t="n">
         <v>25</v>
@@ -29481,13 +29510,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979254</t>
+          <t>https://artportalen.se/Sighting/5979251</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>5979255</v>
+        <v>5979254</v>
       </c>
       <c r="B224" t="n">
         <v>99038</v>
@@ -29513,7 +29542,7 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -29532,10 +29561,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>560943</v>
+        <v>560937</v>
       </c>
       <c r="R224" t="n">
-        <v>6627939</v>
+        <v>6627972</v>
       </c>
       <c r="S224" t="n">
         <v>25</v>
@@ -29597,6 +29626,123 @@
       </c>
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979254</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B225" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S225" t="n">
+        <v>25</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5979255</t>
         </is>
@@ -29827,6 +29973,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ225"/>
+  <dimension ref="A1:AZ230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9258,7 +9258,7 @@
         <v>135225611</v>
       </c>
       <c r="B72" t="n">
-        <v>57280</v>
+        <v>57285</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>134944259</v>
       </c>
       <c r="B79" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>134982406</v>
       </c>
       <c r="B80" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>135031665</v>
       </c>
       <c r="B81" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>135570571</v>
       </c>
       <c r="B119" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>135570663</v>
       </c>
       <c r="B156" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>135570691</v>
       </c>
       <c r="B160" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>135407739</v>
       </c>
       <c r="B187" t="n">
-        <v>56842</v>
+        <v>56847</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>134847157</v>
       </c>
       <c r="B188" t="n">
-        <v>56854</v>
+        <v>56859</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -25018,40 +25018,36 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134845434</v>
+        <v>135605433</v>
       </c>
       <c r="B189" t="n">
-        <v>56833</v>
+        <v>56859</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
@@ -25066,14 +25062,14 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>561038</v>
+        <v>561299</v>
       </c>
       <c r="R189" t="n">
-        <v>6627624</v>
+        <v>6627804</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -25100,27 +25096,27 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Minst 213 ekolokaliseringssekvenser och 32 feeding buzz registrerdes under natten. Arten använder området för födosök.</t>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Pygmépipistrell registrerades vid flera tillfällen under inventeringsperioden, både strax efter skymning och under den senare delen av natten. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -25134,12 +25130,12 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>Sumpskogsomåde</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>
@@ -25156,16 +25152,16 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134845434</t>
+          <t>https://artportalen.se/Sighting/135605433</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>134797837</v>
+        <v>134845434</v>
       </c>
       <c r="B190" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -25188,7 +25184,7 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -25214,10 +25210,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>560991</v>
+        <v>561038</v>
       </c>
       <c r="R190" t="n">
-        <v>6627590</v>
+        <v>6627624</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -25249,22 +25245,22 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Minst 213 ekolokaliseringssekvenser och 32 feeding buzz registrerdes under natten. Arten använder området för födosök.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -25283,7 +25279,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Sumpskogsomåde</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr"/>
@@ -25300,16 +25296,16 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134797837</t>
+          <t>https://artportalen.se/Sighting/134845434</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>135221795</v>
+        <v>134797837</v>
       </c>
       <c r="B191" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -25332,7 +25328,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -25354,14 +25350,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>561104</v>
+        <v>560991</v>
       </c>
       <c r="R191" t="n">
-        <v>6627571</v>
+        <v>6627590</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -25388,27 +25384,27 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -25422,12 +25418,12 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr"/>
@@ -25444,16 +25440,16 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135221795</t>
+          <t>https://artportalen.se/Sighting/134797837</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>135406665</v>
+        <v>135221795</v>
       </c>
       <c r="B192" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -25479,7 +25475,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
@@ -25498,10 +25498,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>561206</v>
+        <v>561104</v>
       </c>
       <c r="R192" t="n">
-        <v>6627647</v>
+        <v>6627571</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -25528,7 +25528,7 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
@@ -25538,17 +25538,17 @@
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>03:16</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr"/>
@@ -25584,16 +25584,16 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135406665</t>
+          <t>https://artportalen.se/Sighting/135221795</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134797963</v>
+        <v>135406665</v>
       </c>
       <c r="B193" t="n">
-        <v>56856</v>
+        <v>56838</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -25601,36 +25601,32 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N193" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -25638,14 +25634,14 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>560991</v>
+        <v>561206</v>
       </c>
       <c r="R193" t="n">
-        <v>6627590</v>
+        <v>6627647</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -25672,27 +25668,27 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>03:16</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25706,12 +25702,12 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -25728,16 +25724,16 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134797963</t>
+          <t>https://artportalen.se/Sighting/135406665</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135221801</v>
+        <v>135605338</v>
       </c>
       <c r="B194" t="n">
-        <v>56856</v>
+        <v>56838</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -25745,36 +25741,28 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N194" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -25786,10 +25774,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>561104</v>
+        <v>561299</v>
       </c>
       <c r="R194" t="n">
-        <v>6627571</v>
+        <v>6627804</v>
       </c>
       <c r="S194" t="n">
         <v>25</v>
@@ -25816,27 +25804,27 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid flera tillfällen under inventeringsperioden, både tidigt på kvällen, omkring midnatt och strax före gryning. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25850,12 +25838,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
@@ -25872,16 +25860,16 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135221801</t>
+          <t>https://artportalen.se/Sighting/135605338</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>91949709</v>
+        <v>134797963</v>
       </c>
       <c r="B195" t="n">
-        <v>56522</v>
+        <v>56861</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -25889,21 +25877,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>206004</v>
+        <v>206002</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -25911,28 +25899,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>561067</v>
+        <v>560991</v>
       </c>
       <c r="R195" t="n">
-        <v>6627551</v>
+        <v>6627590</v>
       </c>
       <c r="S195" t="n">
         <v>25</v>
@@ -25959,27 +25948,27 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Sprang över Skogsmursvägen  helvit</t>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25990,6 +25979,16 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
@@ -26005,16 +26004,16 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91949709</t>
+          <t>https://artportalen.se/Sighting/134797963</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135589893</v>
+        <v>135221801</v>
       </c>
       <c r="B196" t="n">
-        <v>56706</v>
+        <v>56861</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -26022,16 +26021,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>206046</v>
+        <v>206002</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -26044,24 +26043,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -26070,10 +26062,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>561272</v>
+        <v>561104</v>
       </c>
       <c r="R196" t="n">
-        <v>6627729</v>
+        <v>6627571</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -26100,22 +26092,27 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26129,12 +26126,12 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>Hällmarksbarrskog</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>Myrholme</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -26151,67 +26148,67 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135589893</t>
+          <t>https://artportalen.se/Sighting/135221801</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126415504</v>
+        <v>135605416</v>
       </c>
       <c r="B197" t="n">
-        <v>58817</v>
+        <v>56861</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>208249</v>
+        <v>206002</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>561023</v>
+        <v>561299</v>
       </c>
       <c r="R197" t="n">
-        <v>6627575</v>
+        <v>6627804</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -26235,22 +26232,27 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -26259,13 +26261,17 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Hällmarksblandskog</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr"/>
@@ -26282,38 +26288,38 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126415504</t>
+          <t>https://artportalen.se/Sighting/135605416</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118334109</v>
+        <v>91949709</v>
       </c>
       <c r="B198" t="n">
-        <v>99035</v>
+        <v>56522</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -26323,22 +26329,29 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>561057</v>
+        <v>561067</v>
       </c>
       <c r="R198" t="n">
-        <v>6627592</v>
+        <v>6627551</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -26362,22 +26375,27 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Sprang över Skogsmursvägen  helvit</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -26388,11 +26406,6 @@
       </c>
       <c r="AG198" t="b">
         <v>0</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
@@ -26408,38 +26421,38 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118334109</t>
+          <t>https://artportalen.se/Sighting/91949709</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126416641</v>
+        <v>135589893</v>
       </c>
       <c r="B199" t="n">
-        <v>99035</v>
+        <v>56711</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -26449,22 +26462,37 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>561018</v>
+        <v>561272</v>
       </c>
       <c r="R199" t="n">
-        <v>6627875</v>
+        <v>6627729</v>
       </c>
       <c r="S199" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -26488,22 +26516,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -26517,7 +26545,12 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr"/>
@@ -26534,68 +26567,70 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416641</t>
+          <t>https://artportalen.se/Sighting/135589893</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135071078</v>
+        <v>135649870</v>
       </c>
       <c r="B200" t="n">
-        <v>99112</v>
+        <v>56711</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>561117</v>
+        <v>561104</v>
       </c>
       <c r="R200" t="n">
-        <v>6627574</v>
+        <v>6627266</v>
       </c>
       <c r="S200" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -26619,22 +26654,27 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Älgko med fjolårsunge</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -26648,7 +26688,7 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr"/>
@@ -26665,16 +26705,16 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071078</t>
+          <t>https://artportalen.se/Sighting/135649870</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>135147368</v>
+        <v>126415504</v>
       </c>
       <c r="B201" t="n">
-        <v>99112</v>
+        <v>58817</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26682,21 +26722,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -26704,29 +26744,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>561051</v>
+        <v>561023</v>
       </c>
       <c r="R201" t="n">
-        <v>6627607</v>
+        <v>6627575</v>
       </c>
       <c r="S201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -26750,22 +26789,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -26774,8 +26813,14 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -26791,16 +26836,16 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147368</t>
+          <t>https://artportalen.se/Sighting/126415504</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>135147426</v>
+        <v>135660351</v>
       </c>
       <c r="B202" t="n">
-        <v>99112</v>
+        <v>58844</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -26808,43 +26853,51 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>561010</v>
+        <v>561052</v>
       </c>
       <c r="R202" t="n">
-        <v>6627744</v>
+        <v>6627613</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -26871,22 +26924,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26895,6 +26953,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -26917,16 +26976,16 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147426</t>
+          <t>https://artportalen.se/Sighting/135660351</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135147597</v>
+        <v>118334109</v>
       </c>
       <c r="B203" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -26953,12 +27012,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -26968,17 +27022,17 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>561003</v>
+        <v>561057</v>
       </c>
       <c r="R203" t="n">
-        <v>6627860</v>
+        <v>6627592</v>
       </c>
       <c r="S203" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -27002,22 +27056,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27031,7 +27085,7 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr"/>
@@ -27048,16 +27102,16 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147597</t>
+          <t>https://artportalen.se/Sighting/118334109</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135147621</v>
+        <v>126416641</v>
       </c>
       <c r="B204" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -27087,11 +27141,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K204" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -27099,17 +27148,17 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>561005</v>
+        <v>561018</v>
       </c>
       <c r="R204" t="n">
-        <v>6627859</v>
+        <v>6627875</v>
       </c>
       <c r="S204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27133,22 +27182,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27179,68 +27228,68 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147621</t>
+          <t>https://artportalen.se/Sighting/126416641</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>116192832</v>
+        <v>135071078</v>
       </c>
       <c r="B205" t="n">
-        <v>99118</v>
+        <v>99159</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>561001</v>
+        <v>561117</v>
       </c>
       <c r="R205" t="n">
-        <v>6627609</v>
+        <v>6627574</v>
       </c>
       <c r="S205" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27264,22 +27313,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27293,7 +27342,7 @@
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT205" t="inlineStr"/>
@@ -27310,38 +27359,38 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192832</t>
+          <t>https://artportalen.se/Sighting/135071078</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>116196922</v>
+        <v>135147368</v>
       </c>
       <c r="B206" t="n">
-        <v>99118</v>
+        <v>99159</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -27351,29 +27400,27 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>561103</v>
+        <v>561051</v>
       </c>
       <c r="R206" t="n">
-        <v>6627492</v>
+        <v>6627607</v>
       </c>
       <c r="S206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -27397,22 +27444,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -27421,14 +27468,8 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
@@ -27444,74 +27485,63 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116196922</t>
+          <t>https://artportalen.se/Sighting/135147368</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>116377628</v>
+        <v>135147426</v>
       </c>
       <c r="B207" t="n">
-        <v>99118</v>
+        <v>99159</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>560998</v>
+        <v>561010</v>
       </c>
       <c r="R207" t="n">
-        <v>6627569</v>
+        <v>6627744</v>
       </c>
       <c r="S207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -27535,22 +27565,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -27559,7 +27589,6 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -27582,43 +27611,43 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116377628</t>
+          <t>https://artportalen.se/Sighting/135147426</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>123329692</v>
+        <v>135147597</v>
       </c>
       <c r="B208" t="n">
-        <v>99118</v>
+        <v>99159</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -27628,28 +27657,22 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr"/>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>561099</v>
+        <v>561003</v>
       </c>
       <c r="R208" t="n">
-        <v>6627492</v>
+        <v>6627860</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -27673,12 +27696,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -27687,18 +27720,12 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr"/>
@@ -27715,43 +27742,43 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123329692</t>
+          <t>https://artportalen.se/Sighting/135147597</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>132660822</v>
+        <v>135147621</v>
       </c>
       <c r="B209" t="n">
-        <v>99195</v>
+        <v>99159</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -27761,19 +27788,19 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>560999</v>
+        <v>561005</v>
       </c>
       <c r="R209" t="n">
-        <v>6627568</v>
+        <v>6627859</v>
       </c>
       <c r="S209" t="n">
         <v>2</v>
@@ -27800,27 +27827,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27851,54 +27873,68 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132660822</t>
+          <t>https://artportalen.se/Sighting/135147621</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>4221674</v>
+        <v>116192832</v>
       </c>
       <c r="B210" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>561035</v>
+        <v>561001</v>
       </c>
       <c r="R210" t="n">
-        <v>6627874</v>
+        <v>6627609</v>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27922,12 +27958,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27939,73 +27985,89 @@
       <c r="AG210" t="b">
         <v>0</v>
       </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>Tallskog/moränmark</t>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4221674</t>
+          <t>https://artportalen.se/Sighting/116192832</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>4225188</v>
+        <v>116196922</v>
       </c>
       <c r="B211" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561108</v>
+        <v>561103</v>
       </c>
       <c r="R211" t="n">
-        <v>6627497</v>
+        <v>6627492</v>
       </c>
       <c r="S211" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28029,17 +28091,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>sparsam</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28048,65 +28115,78 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
+      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4225188</t>
+          <t>https://artportalen.se/Sighting/116196922</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>99086346</v>
+        <v>116377628</v>
       </c>
       <c r="B212" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
@@ -28115,17 +28195,17 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>561003</v>
+        <v>560998</v>
       </c>
       <c r="R212" t="n">
-        <v>6627635</v>
+        <v>6627569</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28149,12 +28229,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28167,6 +28257,11 @@
       <c r="AG212" t="b">
         <v>0</v>
       </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
@@ -28181,43 +28276,55 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99086346</t>
+          <t>https://artportalen.se/Sighting/116377628</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>104578243</v>
+        <v>123329692</v>
       </c>
       <c r="B213" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr"/>
       <c r="N213" t="inlineStr">
         <is>
@@ -28226,17 +28333,17 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>560987</v>
+        <v>561099</v>
       </c>
       <c r="R213" t="n">
-        <v>6627629</v>
+        <v>6627492</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28260,12 +28367,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28283,6 +28390,11 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
+        </is>
+      </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
@@ -28297,63 +28409,68 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104578243</t>
+          <t>https://artportalen.se/Sighting/123329692</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>116192263</v>
+        <v>132660822</v>
       </c>
       <c r="B214" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>560991</v>
+        <v>560999</v>
       </c>
       <c r="R214" t="n">
-        <v>6627626</v>
+        <v>6627568</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -28377,22 +28494,27 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -28423,13 +28545,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192263</t>
+          <t>https://artportalen.se/Sighting/132660822</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126413111</v>
+        <v>4221674</v>
       </c>
       <c r="B215" t="n">
         <v>97983</v>
@@ -28457,29 +28579,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>561017</v>
+        <v>561035</v>
       </c>
       <c r="R215" t="n">
-        <v>6627814</v>
+        <v>6627874</v>
       </c>
       <c r="S215" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -28503,22 +28616,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -28529,28 +28632,33 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Tallskog/moränmark</t>
+        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413111</t>
+          <t>https://artportalen.se/Sighting/4221674</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>126413356</v>
+        <v>4225188</v>
       </c>
       <c r="B216" t="n">
         <v>97983</v>
@@ -28578,29 +28686,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>561013</v>
+        <v>561108</v>
       </c>
       <c r="R216" t="n">
-        <v>6627677</v>
+        <v>6627497</v>
       </c>
       <c r="S216" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -28624,22 +28723,17 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28651,32 +28745,32 @@
       <c r="AG216" t="b">
         <v>0</v>
       </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413356</t>
+          <t>https://artportalen.se/Sighting/4225188</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126416592</v>
+        <v>99086346</v>
       </c>
       <c r="B217" t="n">
         <v>97983</v>
@@ -28704,29 +28798,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>561027</v>
+        <v>561003</v>
       </c>
       <c r="R217" t="n">
-        <v>6627858</v>
+        <v>6627635</v>
       </c>
       <c r="S217" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -28750,22 +28843,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>17:54</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>17:54</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28774,6 +28857,7 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
+      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -28791,13 +28875,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416592</t>
+          <t>https://artportalen.se/Sighting/99086346</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128162622</v>
+        <v>104578243</v>
       </c>
       <c r="B218" t="n">
         <v>97983</v>
@@ -28825,29 +28909,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>561012</v>
+        <v>560987</v>
       </c>
       <c r="R218" t="n">
-        <v>6627671</v>
+        <v>6627629</v>
       </c>
       <c r="S218" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -28871,22 +28954,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>18:06</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>18:06</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -28895,6 +28968,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -28917,16 +28991,16 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162622</t>
+          <t>https://artportalen.se/Sighting/104578243</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133764984</v>
+        <v>116192263</v>
       </c>
       <c r="B219" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -28953,7 +29027,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -28963,17 +29037,17 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>561227</v>
+        <v>560991</v>
       </c>
       <c r="R219" t="n">
-        <v>6627267</v>
+        <v>6627626</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -28997,22 +29071,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29043,16 +29117,16 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133764984</t>
+          <t>https://artportalen.se/Sighting/116192263</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>112959278</v>
+        <v>126413111</v>
       </c>
       <c r="B220" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -29060,16 +29134,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -29077,28 +29151,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>561019</v>
+        <v>561017</v>
       </c>
       <c r="R220" t="n">
-        <v>6627490</v>
+        <v>6627814</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29122,12 +29197,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29136,7 +29221,6 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -29154,16 +29238,16 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959278</t>
+          <t>https://artportalen.se/Sighting/126413111</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134063381</v>
+        <v>126413356</v>
       </c>
       <c r="B221" t="n">
-        <v>99472</v>
+        <v>97983</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -29171,16 +29255,16 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -29188,25 +29272,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>560964</v>
+        <v>561013</v>
       </c>
       <c r="R221" t="n">
-        <v>6627632</v>
+        <v>6627677</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29230,22 +29318,22 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29276,16 +29364,16 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134063381</t>
+          <t>https://artportalen.se/Sighting/126413356</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>5979250</v>
+        <v>126416592</v>
       </c>
       <c r="B222" t="n">
-        <v>99038</v>
+        <v>97983</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -29293,47 +29381,46 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>560984</v>
+        <v>561027</v>
       </c>
       <c r="R222" t="n">
-        <v>6627735</v>
+        <v>6627858</v>
       </c>
       <c r="S222" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29357,12 +29444,22 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29373,36 +29470,31 @@
       </c>
       <c r="AG222" t="b">
         <v>0</v>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979250</t>
+          <t>https://artportalen.se/Sighting/126416592</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>5979251</v>
+        <v>128162622</v>
       </c>
       <c r="B223" t="n">
-        <v>99038</v>
+        <v>97983</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -29410,47 +29502,46 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>560967</v>
+        <v>561012</v>
       </c>
       <c r="R223" t="n">
-        <v>6627698</v>
+        <v>6627671</v>
       </c>
       <c r="S223" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -29474,12 +29565,22 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -29491,35 +29592,35 @@
       <c r="AG223" t="b">
         <v>0</v>
       </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979251</t>
+          <t>https://artportalen.se/Sighting/128162622</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>5979254</v>
+        <v>133764984</v>
       </c>
       <c r="B224" t="n">
-        <v>99038</v>
+        <v>98060</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -29527,47 +29628,46 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>560937</v>
+        <v>561227</v>
       </c>
       <c r="R224" t="n">
-        <v>6627972</v>
+        <v>6627267</v>
       </c>
       <c r="S224" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -29591,12 +29691,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29608,35 +29718,35 @@
       <c r="AG224" t="b">
         <v>0</v>
       </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979254</t>
+          <t>https://artportalen.se/Sighting/133764984</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>5979255</v>
+        <v>112959278</v>
       </c>
       <c r="B225" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -29644,44 +29754,42 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>560943</v>
+        <v>561019</v>
       </c>
       <c r="R225" t="n">
-        <v>6627939</v>
+        <v>6627490</v>
       </c>
       <c r="S225" t="n">
         <v>25</v>
@@ -29708,12 +29816,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -29722,27 +29830,613 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112959278</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>134063381</v>
+      </c>
+      <c r="B226" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>560964</v>
+      </c>
+      <c r="R226" t="n">
+        <v>6627632</v>
+      </c>
+      <c r="S226" t="n">
+        <v>5</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134063381</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>5979250</v>
+      </c>
+      <c r="B227" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>560984</v>
+      </c>
+      <c r="R227" t="n">
+        <v>6627735</v>
+      </c>
+      <c r="S227" t="n">
+        <v>25</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979250</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>5979251</v>
+      </c>
+      <c r="B228" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>560967</v>
+      </c>
+      <c r="R228" t="n">
+        <v>6627698</v>
+      </c>
+      <c r="S228" t="n">
+        <v>25</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979251</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B229" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R229" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S229" t="n">
+        <v>25</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979254</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B230" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S230" t="n">
+        <v>25</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5979255</t>
         </is>
@@ -29974,6 +30668,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -27237,7 +27237,7 @@
         <v>135071078</v>
       </c>
       <c r="B205" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>135147368</v>
       </c>
       <c r="B206" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>135147426</v>
       </c>
       <c r="B207" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>135147597</v>
       </c>
       <c r="B208" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>135147621</v>
       </c>
       <c r="B209" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>135225611</v>
       </c>
       <c r="B72" t="n">
-        <v>57285</v>
+        <v>57287</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136014972</v>
       </c>
       <c r="B73" t="n">
-        <v>56854</v>
+        <v>56856</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>135570571</v>
       </c>
       <c r="B119" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>135570663</v>
       </c>
       <c r="B156" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>135570691</v>
       </c>
       <c r="B160" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>135407739</v>
       </c>
       <c r="B187" t="n">
-        <v>56847</v>
+        <v>56849</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>135605433</v>
       </c>
       <c r="B189" t="n">
-        <v>56859</v>
+        <v>56861</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>136014966</v>
       </c>
       <c r="B190" t="n">
-        <v>56859</v>
+        <v>56861</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>134845434</v>
       </c>
       <c r="B191" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>134797837</v>
       </c>
       <c r="B192" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>135221795</v>
       </c>
       <c r="B193" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>135406665</v>
       </c>
       <c r="B194" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>135605338</v>
       </c>
       <c r="B195" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>136014802</v>
       </c>
       <c r="B196" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>135605416</v>
       </c>
       <c r="B199" t="n">
-        <v>56861</v>
+        <v>56863</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>136014962</v>
       </c>
       <c r="B200" t="n">
-        <v>56861</v>
+        <v>56863</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>135589893</v>
       </c>
       <c r="B202" t="n">
-        <v>56711</v>
+        <v>56713</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>135649870</v>
       </c>
       <c r="B203" t="n">
-        <v>56711</v>
+        <v>56713</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>135660351</v>
       </c>
       <c r="B205" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ234"/>
+  <dimension ref="A1:AZ238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21078,32 +21078,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133938205</v>
+        <v>136168846</v>
       </c>
       <c r="B158" t="n">
-        <v>58131</v>
+        <v>58143</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -21111,31 +21111,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm , Skogen V om Salsmossen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>560966</v>
+        <v>561087</v>
       </c>
       <c r="R158" t="n">
-        <v>6627675</v>
+        <v>6627796</v>
       </c>
       <c r="S158" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -21159,22 +21157,22 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -21185,6 +21183,11 @@
       </c>
       <c r="AG158" t="b">
         <v>0</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
@@ -21200,13 +21203,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133938205</t>
+          <t>https://artportalen.se/Sighting/136168846</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132468178</v>
+        <v>133938205</v>
       </c>
       <c r="B159" t="n">
         <v>58131</v>
@@ -21239,24 +21242,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmossen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>561088</v>
+        <v>560966</v>
       </c>
       <c r="R159" t="n">
-        <v>6627651</v>
+        <v>6627675</v>
       </c>
       <c r="S159" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -21280,22 +21290,22 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -21306,11 +21316,6 @@
       </c>
       <c r="AG159" t="b">
         <v>0</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
@@ -21326,13 +21331,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132468178</t>
+          <t>https://artportalen.se/Sighting/133938205</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133277288</v>
+        <v>132468178</v>
       </c>
       <c r="B160" t="n">
         <v>58131</v>
@@ -21362,32 +21367,27 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>561055</v>
+        <v>561088</v>
       </c>
       <c r="R160" t="n">
-        <v>6627529</v>
+        <v>6627651</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -21411,22 +21411,22 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -21457,16 +21457,16 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133277288</t>
+          <t>https://artportalen.se/Sighting/132468178</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135570691</v>
+        <v>133277288</v>
       </c>
       <c r="B161" t="n">
-        <v>58138</v>
+        <v>58131</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -21501,30 +21501,24 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>561282</v>
+        <v>561055</v>
       </c>
       <c r="R161" t="n">
-        <v>6627823</v>
+        <v>6627529</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -21548,22 +21542,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -21577,12 +21571,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>Myrholme</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr"/>
@@ -21599,33 +21588,33 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135570691</t>
+          <t>https://artportalen.se/Sighting/133277288</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>124170153</v>
+        <v>135570691</v>
       </c>
       <c r="B162" t="n">
-        <v>58602</v>
+        <v>58138</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -21635,7 +21624,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -21643,24 +21632,30 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Skogsmuren, Ramnäs, Vstm, Skogsmuren, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>561169</v>
+        <v>561282</v>
       </c>
       <c r="R162" t="n">
-        <v>6627457</v>
+        <v>6627823</v>
       </c>
       <c r="S162" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -21684,22 +21679,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -21710,6 +21705,16 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
@@ -21725,33 +21730,33 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124170153</t>
+          <t>https://artportalen.se/Sighting/135570691</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126142060</v>
+        <v>136168858</v>
       </c>
       <c r="B163" t="n">
-        <v>58602</v>
+        <v>58138</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -21769,26 +21774,24 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm , Skogen V om Salsmossen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>561032</v>
+        <v>561085</v>
       </c>
       <c r="R163" t="n">
-        <v>6627610</v>
+        <v>6627794</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -21812,22 +21815,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -21858,13 +21861,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126142060</t>
+          <t>https://artportalen.se/Sighting/136168858</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126416189</v>
+        <v>124170153</v>
       </c>
       <c r="B164" t="n">
         <v>58602</v>
@@ -21904,22 +21907,22 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogsmuren, Ramnäs, Vstm, Skogsmuren, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>561024</v>
+        <v>561169</v>
       </c>
       <c r="R164" t="n">
-        <v>6627581</v>
+        <v>6627457</v>
       </c>
       <c r="S164" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -21943,22 +21946,22 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -21969,11 +21972,6 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -21989,13 +21987,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416189</t>
+          <t>https://artportalen.se/Sighting/124170153</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129344266</v>
+        <v>126142060</v>
       </c>
       <c r="B165" t="n">
         <v>58602</v>
@@ -22025,7 +22023,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -22042,17 +22040,17 @@
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>561215</v>
+        <v>561032</v>
       </c>
       <c r="R165" t="n">
-        <v>6627683</v>
+        <v>6627610</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -22076,22 +22074,22 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -22122,16 +22120,16 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129344266</t>
+          <t>https://artportalen.se/Sighting/126142060</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>134063345</v>
+        <v>126416189</v>
       </c>
       <c r="B166" t="n">
-        <v>58624</v>
+        <v>58602</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -22158,24 +22156,29 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>560966</v>
+        <v>561024</v>
       </c>
       <c r="R166" t="n">
-        <v>6627621</v>
+        <v>6627581</v>
       </c>
       <c r="S166" t="n">
         <v>50</v>
@@ -22202,22 +22205,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -22228,6 +22231,11 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
@@ -22243,71 +22251,70 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134063345</t>
+          <t>https://artportalen.se/Sighting/126416189</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>72718115</v>
+        <v>129344266</v>
       </c>
       <c r="B167" t="n">
-        <v>8455</v>
+        <v>58602</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Skogen ö Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>560995</v>
+        <v>561215</v>
       </c>
       <c r="R167" t="n">
-        <v>6627487</v>
+        <v>6627683</v>
       </c>
       <c r="S167" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -22331,22 +22338,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2018-08-16</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2018-08-16</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -22355,23 +22362,12 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>Trädbas</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Tree base # Tall</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
@@ -22388,38 +22384,38 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72718115</t>
+          <t>https://artportalen.se/Sighting/129344266</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>72718136</v>
+        <v>134063345</v>
       </c>
       <c r="B168" t="n">
-        <v>8455</v>
+        <v>58624</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>106545</v>
+        <v>103042</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -22427,32 +22423,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>560976</v>
+        <v>560966</v>
       </c>
       <c r="R168" t="n">
-        <v>6627819</v>
+        <v>6627621</v>
       </c>
       <c r="S168" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -22476,22 +22464,22 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2018-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2018-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -22500,24 +22488,8 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Tall</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -22533,13 +22505,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72718136</t>
+          <t>https://artportalen.se/Sighting/134063345</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>73098715</v>
+        <v>72718115</v>
       </c>
       <c r="B169" t="n">
         <v>8455</v>
@@ -22567,7 +22539,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
@@ -22583,14 +22559,14 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen ö Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>561081</v>
+        <v>560995</v>
       </c>
       <c r="R169" t="n">
-        <v>6627774</v>
+        <v>6627487</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -22617,22 +22593,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -22645,6 +22621,21 @@
       <c r="AG169" t="b">
         <v>0</v>
       </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Trädbas</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Tree base # Tall</t>
+        </is>
+      </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
@@ -22659,13 +22650,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73098715</t>
+          <t>https://artportalen.se/Sighting/72718115</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>73098733</v>
+        <v>72718136</v>
       </c>
       <c r="B170" t="n">
         <v>8455</v>
@@ -22693,7 +22684,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
@@ -22709,14 +22704,14 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>561082</v>
+        <v>560976</v>
       </c>
       <c r="R170" t="n">
-        <v>6627681</v>
+        <v>6627819</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -22743,22 +22738,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -22771,6 +22766,21 @@
       <c r="AG170" t="b">
         <v>0</v>
       </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Tall</t>
+        </is>
+      </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
@@ -22785,13 +22795,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73098733</t>
+          <t>https://artportalen.se/Sighting/72718136</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>99069013</v>
+        <v>73098715</v>
       </c>
       <c r="B171" t="n">
         <v>8455</v>
@@ -22828,17 +22838,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>561002</v>
+        <v>561081</v>
       </c>
       <c r="R171" t="n">
-        <v>6627839</v>
+        <v>6627774</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -22865,12 +22879,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2018-09-12</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2018-09-12</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22897,13 +22921,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99069013</t>
+          <t>https://artportalen.se/Sighting/73098715</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>103876354</v>
+        <v>73098733</v>
       </c>
       <c r="B172" t="n">
         <v>8455</v>
@@ -22940,20 +22964,24 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>561076</v>
+        <v>561082</v>
       </c>
       <c r="R172" t="n">
-        <v>6627945</v>
+        <v>6627681</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -22977,22 +23005,22 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -23005,11 +23033,6 @@
       <c r="AG172" t="b">
         <v>0</v>
       </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
@@ -23024,13 +23047,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103876354</t>
+          <t>https://artportalen.se/Sighting/73098733</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>103876451</v>
+        <v>99069013</v>
       </c>
       <c r="B173" t="n">
         <v>8455</v>
@@ -23070,17 +23093,17 @@
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>561118</v>
+        <v>561002</v>
       </c>
       <c r="R173" t="n">
-        <v>6627873</v>
+        <v>6627839</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -23104,22 +23127,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -23132,11 +23145,6 @@
       <c r="AG173" t="b">
         <v>0</v>
       </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
@@ -23151,13 +23159,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103876451</t>
+          <t>https://artportalen.se/Sighting/99069013</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>103877642</v>
+        <v>103876354</v>
       </c>
       <c r="B174" t="n">
         <v>8455</v>
@@ -23201,13 +23209,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>561215</v>
+        <v>561076</v>
       </c>
       <c r="R174" t="n">
-        <v>6627683</v>
+        <v>6627945</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -23236,7 +23244,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -23246,7 +23254,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -23278,13 +23286,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103877642</t>
+          <t>https://artportalen.se/Sighting/103876354</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>103877747</v>
+        <v>103876451</v>
       </c>
       <c r="B175" t="n">
         <v>8455</v>
@@ -23328,13 +23336,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>561150</v>
+        <v>561118</v>
       </c>
       <c r="R175" t="n">
-        <v>6627640</v>
+        <v>6627873</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -23363,7 +23371,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -23373,7 +23381,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -23405,13 +23413,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103877747</t>
+          <t>https://artportalen.se/Sighting/103876451</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>110818218</v>
+        <v>103877642</v>
       </c>
       <c r="B176" t="n">
         <v>8455</v>
@@ -23451,17 +23459,17 @@
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Salsmossen, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>561105</v>
+        <v>561215</v>
       </c>
       <c r="R176" t="n">
-        <v>6627876</v>
+        <v>6627683</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -23485,12 +23493,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -23503,37 +23521,32 @@
       <c r="AG176" t="b">
         <v>0</v>
       </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>Tall</t>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110818218</t>
+          <t>https://artportalen.se/Sighting/103877642</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>112959116</v>
+        <v>103877747</v>
       </c>
       <c r="B177" t="n">
         <v>8455</v>
@@ -23570,24 +23583,20 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>561071</v>
+        <v>561150</v>
       </c>
       <c r="R177" t="n">
-        <v>6627396</v>
+        <v>6627640</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -23611,12 +23620,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -23648,13 +23667,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959116</t>
+          <t>https://artportalen.se/Sighting/103877747</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>112959135</v>
+        <v>110818218</v>
       </c>
       <c r="B178" t="n">
         <v>8455</v>
@@ -23691,21 +23710,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Salsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>561063</v>
+        <v>561105</v>
       </c>
       <c r="R178" t="n">
-        <v>6627421</v>
+        <v>6627876</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -23732,12 +23747,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23750,27 +23765,37 @@
       <c r="AG178" t="b">
         <v>0</v>
       </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959135</t>
+          <t>https://artportalen.se/Sighting/110818218</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>112959160</v>
+        <v>112959116</v>
       </c>
       <c r="B179" t="n">
         <v>8455</v>
@@ -23818,10 +23843,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>561095</v>
+        <v>561071</v>
       </c>
       <c r="R179" t="n">
-        <v>6627370</v>
+        <v>6627396</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -23866,6 +23891,11 @@
       <c r="AG179" t="b">
         <v>0</v>
       </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
@@ -23880,13 +23910,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959160</t>
+          <t>https://artportalen.se/Sighting/112959116</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>112959251</v>
+        <v>112959135</v>
       </c>
       <c r="B180" t="n">
         <v>8455</v>
@@ -23934,10 +23964,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>561090</v>
+        <v>561063</v>
       </c>
       <c r="R180" t="n">
-        <v>6627383</v>
+        <v>6627421</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -23996,13 +24026,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959251</t>
+          <t>https://artportalen.se/Sighting/112959135</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>116519463</v>
+        <v>112959160</v>
       </c>
       <c r="B181" t="n">
         <v>8455</v>
@@ -24031,24 +24061,32 @@
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>561116</v>
+        <v>561095</v>
       </c>
       <c r="R181" t="n">
-        <v>6627877</v>
+        <v>6627370</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -24072,22 +24110,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -24096,13 +24124,9 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
@@ -24118,13 +24142,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116519463</t>
+          <t>https://artportalen.se/Sighting/112959160</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119486009</v>
+        <v>112959251</v>
       </c>
       <c r="B182" t="n">
         <v>8455</v>
@@ -24161,20 +24185,24 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Salsmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>561248</v>
+        <v>561090</v>
       </c>
       <c r="R182" t="n">
-        <v>6627447</v>
+        <v>6627383</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -24198,12 +24226,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -24216,37 +24244,27 @@
       <c r="AG182" t="b">
         <v>0</v>
       </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119486009</t>
+          <t>https://artportalen.se/Sighting/112959251</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120768887</v>
+        <v>116519463</v>
       </c>
       <c r="B183" t="n">
         <v>8455</v>
@@ -24275,32 +24293,24 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>561108</v>
+        <v>561116</v>
       </c>
       <c r="R183" t="n">
-        <v>6627916</v>
+        <v>6627877</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -24324,22 +24334,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -24348,7 +24358,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -24371,13 +24380,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120768887</t>
+          <t>https://artportalen.se/Sighting/116519463</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129294056</v>
+        <v>119486009</v>
       </c>
       <c r="B184" t="n">
         <v>8455</v>
@@ -24406,21 +24415,25 @@
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
+          <t>Salsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>561078</v>
+        <v>561248</v>
       </c>
       <c r="R184" t="n">
-        <v>6627826</v>
+        <v>6627447</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -24447,27 +24460,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Tall som fallit på Salsmossen</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -24476,35 +24474,41 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129294056</t>
+          <t>https://artportalen.se/Sighting/119486009</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129294401</v>
+        <v>120768887</v>
       </c>
       <c r="B185" t="n">
         <v>8455</v>
@@ -24533,19 +24537,32 @@
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>561104</v>
+        <v>561108</v>
       </c>
       <c r="R185" t="n">
-        <v>6627876</v>
+        <v>6627916</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -24569,22 +24586,22 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -24593,6 +24610,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -24615,16 +24633,16 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129294401</t>
+          <t>https://artportalen.se/Sighting/120768887</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>132663002</v>
+        <v>129294056</v>
       </c>
       <c r="B186" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -24661,13 +24679,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>561067</v>
+        <v>561078</v>
       </c>
       <c r="R186" t="n">
-        <v>6627834</v>
+        <v>6627826</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -24691,22 +24709,27 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Tall som fallit på Salsmossen</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24720,7 +24743,7 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Våtmark</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -24737,16 +24760,16 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132663002</t>
+          <t>https://artportalen.se/Sighting/129294056</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>134259194</v>
+        <v>129294401</v>
       </c>
       <c r="B187" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -24772,24 +24795,19 @@
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Salsmossen, Ramnäs, Salsmossen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>561205</v>
+        <v>561104</v>
       </c>
       <c r="R187" t="n">
-        <v>6627726</v>
+        <v>6627876</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -24813,27 +24831,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -24864,16 +24877,16 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134259194</t>
+          <t>https://artportalen.se/Sighting/129294401</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>135407739</v>
+        <v>132663002</v>
       </c>
       <c r="B188" t="n">
-        <v>56849</v>
+        <v>8460</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -24881,54 +24894,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>205992</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Salsmossen, Ramnäs, Vstmmn , Skogen V om Salsmossen, Ramnäs, Vstmmn , Vstm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>561206</v>
+        <v>561067</v>
       </c>
       <c r="R188" t="n">
-        <v>6627647</v>
+        <v>6627834</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -24952,27 +24953,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>03:16</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24986,12 +24982,7 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -25008,16 +24999,16 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135407739</t>
+          <t>https://artportalen.se/Sighting/132663002</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>134847157</v>
+        <v>134259194</v>
       </c>
       <c r="B189" t="n">
-        <v>56859</v>
+        <v>8460</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -25025,54 +25016,42 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>205995</v>
+        <v>106545</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmossen, Ramnäs, Salsmossen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>560991</v>
+        <v>561205</v>
       </c>
       <c r="R189" t="n">
-        <v>6627590</v>
+        <v>6627726</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -25096,27 +25075,27 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -25131,11 +25110,6 @@
       <c r="AH189" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>
@@ -25152,16 +25126,16 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134847157</t>
+          <t>https://artportalen.se/Sighting/134259194</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>135605433</v>
+        <v>136169020</v>
       </c>
       <c r="B190" t="n">
-        <v>56861</v>
+        <v>8463</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -25169,21 +25143,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>205995</v>
+        <v>106545</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -25192,27 +25166,27 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm , Salsmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>561299</v>
+        <v>561114</v>
       </c>
       <c r="R190" t="n">
-        <v>6627804</v>
+        <v>6627883</v>
       </c>
       <c r="S190" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -25236,27 +25210,22 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Pygmépipistrell registrerades vid flera tillfällen under inventeringsperioden, både strax efter skymning och under den senare delen av natten. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -25265,17 +25234,13 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>Hällmarksblandskog</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>Myrholme med öppet sumpskogsparti</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr"/>
@@ -25292,16 +25257,16 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605433</t>
+          <t>https://artportalen.se/Sighting/136169020</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>136014966</v>
+        <v>135407739</v>
       </c>
       <c r="B191" t="n">
-        <v>56861</v>
+        <v>56849</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -25309,24 +25274,28 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
@@ -25342,14 +25311,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>560990</v>
+        <v>561206</v>
       </c>
       <c r="R191" t="n">
-        <v>6627589</v>
+        <v>6627647</v>
       </c>
       <c r="S191" t="n">
         <v>25</v>
@@ -25376,7 +25345,7 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
@@ -25386,17 +25355,17 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>03:16</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Registrerad med autobox (384 kHz) under nätterna mellan 16–19 augusti, med flera registreringar den 18 augusti, både efter midnatt och under sen kväll (vid ett-tiden på natten samt mellan ca 21:40 och 22:45). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som dvärgpipistrell med hög sannolikhet.</t>
+          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -25410,12 +25379,12 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
+          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr"/>
@@ -25432,39 +25401,43 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136014966</t>
+          <t>https://artportalen.se/Sighting/135407739</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>134845434</v>
+        <v>134847157</v>
       </c>
       <c r="B192" t="n">
-        <v>56840</v>
+        <v>56859</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -25474,11 +25447,7 @@
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -25490,10 +25459,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>561038</v>
+        <v>560991</v>
       </c>
       <c r="R192" t="n">
-        <v>6627624</v>
+        <v>6627590</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -25525,22 +25494,22 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Minst 213 ekolokaliseringssekvenser och 32 feeding buzz registrerdes under natten. Arten använder området för födosök.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -25559,7 +25528,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>Sumpskogsomåde</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr"/>
@@ -25576,46 +25545,42 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134845434</t>
+          <t>https://artportalen.se/Sighting/134847157</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>134797837</v>
+        <v>135605433</v>
       </c>
       <c r="B193" t="n">
-        <v>56840</v>
+        <v>56861</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
@@ -25630,14 +25595,14 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>560991</v>
+        <v>561299</v>
       </c>
       <c r="R193" t="n">
-        <v>6627590</v>
+        <v>6627804</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -25664,27 +25629,27 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Pygmépipistrell registrerades vid flera tillfällen under inventeringsperioden, både strax efter skymning och under den senare delen av natten. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25698,12 +25663,12 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -25720,46 +25685,42 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134797837</t>
+          <t>https://artportalen.se/Sighting/135605433</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>135221795</v>
+        <v>136014966</v>
       </c>
       <c r="B194" t="n">
-        <v>56840</v>
+        <v>56861</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
@@ -25774,14 +25735,14 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>561104</v>
+        <v>560990</v>
       </c>
       <c r="R194" t="n">
-        <v>6627571</v>
+        <v>6627589</v>
       </c>
       <c r="S194" t="n">
         <v>25</v>
@@ -25808,7 +25769,7 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
@@ -25818,17 +25779,17 @@
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
+          <t>Registrerad med autobox (384 kHz) under nätterna mellan 16–19 augusti, med flera registreringar den 18 augusti, både efter midnatt och under sen kväll (vid ett-tiden på natten samt mellan ca 21:40 och 22:45). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som dvärgpipistrell med hög sannolikhet.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25842,12 +25803,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>
@@ -25864,13 +25825,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135221795</t>
+          <t>https://artportalen.se/Sighting/136014966</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>135406665</v>
+        <v>134845434</v>
       </c>
       <c r="B195" t="n">
         <v>56840</v>
@@ -25896,10 +25857,14 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
@@ -25914,14 +25879,14 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>561206</v>
+        <v>561038</v>
       </c>
       <c r="R195" t="n">
-        <v>6627647</v>
+        <v>6627624</v>
       </c>
       <c r="S195" t="n">
         <v>25</v>
@@ -25948,27 +25913,27 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>03:16</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Minst 213 ekolokaliseringssekvenser och 32 feeding buzz registrerdes under natten. Arten använder området för födosök.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25982,12 +25947,12 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
+          <t>Sumpskogsomåde</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr"/>
@@ -26004,13 +25969,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135406665</t>
+          <t>https://artportalen.se/Sighting/134845434</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135605338</v>
+        <v>134797837</v>
       </c>
       <c r="B196" t="n">
         <v>56840</v>
@@ -26034,8 +25999,16 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
@@ -26050,14 +26023,14 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>561299</v>
+        <v>560991</v>
       </c>
       <c r="R196" t="n">
-        <v>6627804</v>
+        <v>6627590</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -26084,27 +26057,27 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid flera tillfällen under inventeringsperioden, både tidigt på kvällen, omkring midnatt och strax före gryning. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
+          <t>Inspelning med automatisk ultraljudsdetektor, analyserad i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras. Ekolokaliseringssekvenser.</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26118,12 +26091,12 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>Hällmarksblandskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>Myrholme med öppet sumpskogsparti</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr"/>
@@ -26140,13 +26113,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605338</t>
+          <t>https://artportalen.se/Sighting/134797837</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>136014802</v>
+        <v>135221795</v>
       </c>
       <c r="B197" t="n">
         <v>56840</v>
@@ -26170,8 +26143,16 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
@@ -26186,14 +26167,14 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>560990</v>
+        <v>561104</v>
       </c>
       <c r="R197" t="n">
-        <v>6627589</v>
+        <v>6627571</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -26220,7 +26201,7 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
@@ -26230,17 +26211,17 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Registrerad med autobox (384 kHz) vid bäckmiljö under nätterna 16–19 augusti. Nordfladdermus registrerades den 18 augusti vid ett-tiden på natten. Inspelningen analyserades med BTO Acoustic Pipeline och klassificerades som nordfladdermus med hög sannolikhet.</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Nordfladdermus registrerades återkommande under inventeringsperioden 15–17 juli med mycket hög klassificeringssäkerhet (upp till 0,99). Ett stort antal ekolokaliseringssekvenser registrerades, vilket visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -26254,12 +26235,12 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>Invid bäcken som mynnar ut till Murmossen</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr"/>
@@ -26276,16 +26257,16 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136014802</t>
+          <t>https://artportalen.se/Sighting/135221795</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>134797963</v>
+        <v>135406665</v>
       </c>
       <c r="B198" t="n">
-        <v>56861</v>
+        <v>56840</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -26293,36 +26274,32 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N198" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -26330,14 +26307,14 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>560991</v>
+        <v>561206</v>
       </c>
       <c r="R198" t="n">
-        <v>6627590</v>
+        <v>6627647</v>
       </c>
       <c r="S198" t="n">
         <v>25</v>
@@ -26364,27 +26341,27 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>03:16</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
+          <t>Autobox med ultraljudsdetektor (Raspberry Pi Pico). Inspelningarna analyserades med BTO Acoustic Pipeline. Rapporten avser en sammanfattad observation under inventeringsperioden.</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -26398,12 +26375,12 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
+          <t>Talldominerad barrsumpskog. Intill ligger en blockrik höjd med blandskog och död ved.</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr"/>
@@ -26420,16 +26397,16 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134797963</t>
+          <t>https://artportalen.se/Sighting/135406665</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>135221801</v>
+        <v>135605338</v>
       </c>
       <c r="B199" t="n">
-        <v>56861</v>
+        <v>56840</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -26437,36 +26414,28 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="N199" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -26478,10 +26447,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>561104</v>
+        <v>561299</v>
       </c>
       <c r="R199" t="n">
-        <v>6627571</v>
+        <v>6627804</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -26508,27 +26477,27 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid flera tillfällen under inventeringsperioden, både tidigt på kvällen, omkring midnatt och strax före gryning. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -26542,12 +26511,12 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr"/>
@@ -26564,16 +26533,16 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135221801</t>
+          <t>https://artportalen.se/Sighting/135605338</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>135605416</v>
+        <v>136014802</v>
       </c>
       <c r="B200" t="n">
-        <v>56863</v>
+        <v>56840</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -26581,23 +26550,19 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
@@ -26614,14 +26579,14 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>561299</v>
+        <v>560990</v>
       </c>
       <c r="R200" t="n">
-        <v>6627804</v>
+        <v>6627589</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -26648,17 +26613,17 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
@@ -26668,7 +26633,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
+          <t>Registrerad med autobox (384 kHz) vid bäckmiljö under nätterna 16–19 augusti. Nordfladdermus registrerades den 18 augusti vid ett-tiden på natten. Inspelningen analyserades med BTO Acoustic Pipeline och klassificerades som nordfladdermus med hög sannolikhet.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -26682,12 +26647,12 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>Hällmarksblandskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>Myrholme med öppet sumpskogsparti</t>
+          <t>Invid bäcken som mynnar ut till Murmossen</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr"/>
@@ -26704,16 +26669,16 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605416</t>
+          <t>https://artportalen.se/Sighting/136014802</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>136014962</v>
+        <v>134797963</v>
       </c>
       <c r="B201" t="n">
-        <v>56863</v>
+        <v>56861</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26738,15 +26703,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -26758,10 +26727,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>560990</v>
+        <v>560991</v>
       </c>
       <c r="R201" t="n">
-        <v>6627589</v>
+        <v>6627590</v>
       </c>
       <c r="S201" t="n">
         <v>25</v>
@@ -26788,27 +26757,27 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Registrerad vid upprepade tillfällen med autobox (384 kHz) under nätterna mellan 16–19 augusti, med registreringar från sen kväll till efter midnatt (ca kl. 22:45–02:34). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som brunlångöra med hög sannolikhet.</t>
+          <t>Automatisk ultraljudsdetektor baserad på Raspberry Pi Pico. Analys utförd i BTO Acoustic Pipeline. Endast registreringar med hög sannolikhet rapporteras.</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -26827,7 +26796,7 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog. Genom området rinner en bäck med utflöde till Murmossen.</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr"/>
@@ -26844,16 +26813,16 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136014962</t>
+          <t>https://artportalen.se/Sighting/134797963</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>91949709</v>
+        <v>135221801</v>
       </c>
       <c r="B202" t="n">
-        <v>56522</v>
+        <v>56861</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -26861,21 +26830,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>206004</v>
+        <v>206002</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -26883,28 +26852,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>561067</v>
+        <v>561104</v>
       </c>
       <c r="R202" t="n">
-        <v>6627551</v>
+        <v>6627571</v>
       </c>
       <c r="S202" t="n">
         <v>25</v>
@@ -26931,27 +26901,27 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Sprang över Skogsmursvägen  helvit</t>
+          <t>Automatisk ultraljudsdetektor (Raspberry Pi Pico) analyserad i BTO Acoustic Pipeline. Endast registreringar som efter manuell granskning bedömts ha hög tillförlitlighet har rapporterats. Brunlångöra registrerades återkommande under perioden 15–17 juli med hög klassificeringssäkerhet (upp till 0,95). Fynden visar att arten regelbundet använder området.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26962,6 +26932,16 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>Talldominerad barrsumpskog (kärrskog) med inslag av gran, angränsande till äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
@@ -26977,16 +26957,16 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91949709</t>
+          <t>https://artportalen.se/Sighting/135221801</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>135589893</v>
+        <v>135605416</v>
       </c>
       <c r="B203" t="n">
-        <v>56713</v>
+        <v>56863</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -26994,16 +26974,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>206046</v>
+        <v>206002</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -27011,29 +26991,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -27042,10 +27011,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>561272</v>
+        <v>561299</v>
       </c>
       <c r="R203" t="n">
-        <v>6627729</v>
+        <v>6627804</v>
       </c>
       <c r="S203" t="n">
         <v>25</v>
@@ -27072,22 +27041,27 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Registrering med autobox (384 kHz) under perioden 28 juli–1 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Brun långöra registrerades vid flera tillfällen under inventeringsperioden, främst omkring midnatt och under de tidiga morgontimmarna. Registreringarna tyder på att lokalen används som födosöksområde. Ljudboxen var placerad på en myrholme i Salsmossen med gles äldre tallskog, fuktigt markskikt och inslag av björk. I en öppen mossglänta observerades rikligt med nattflygande insekter under kvällstid. Övergångszonen mellan mossgläntan och den glesa barrskogen utgör en sannolik födosöksmiljö för fladdermöss.</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27101,12 +27075,12 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>Hällmarksbarrskog</t>
+          <t>Hällmarksblandskog</t>
         </is>
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>Myrholme</t>
+          <t>Myrholme med öppet sumpskogsparti</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr"/>
@@ -27123,16 +27097,16 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135589893</t>
+          <t>https://artportalen.se/Sighting/135605416</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>135649870</v>
+        <v>136014962</v>
       </c>
       <c r="B204" t="n">
-        <v>56713</v>
+        <v>56863</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -27140,16 +27114,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>206046</v>
+        <v>206002</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -27157,33 +27131,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>561104</v>
+        <v>560990</v>
       </c>
       <c r="R204" t="n">
-        <v>6627266</v>
+        <v>6627589</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -27210,27 +27181,27 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Älgko med fjolårsunge</t>
+          <t>Registrerad vid upprepade tillfällen med autobox (384 kHz) under nätterna mellan 16–19 augusti, med registreringar från sen kväll till efter midnatt (ca kl. 22:45–02:34). Inspelningarna analyserades med BTO Acoustic Pipeline och klassificerades som brunlångöra med hög sannolikhet.</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27245,6 +27216,11 @@
       <c r="AH204" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>Övergångszon (ekoton) mellan barrskog och öppen mosse.</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr"/>
@@ -27261,33 +27237,33 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135649870</t>
+          <t>https://artportalen.se/Sighting/136014962</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126415504</v>
+        <v>91949709</v>
       </c>
       <c r="B205" t="n">
-        <v>58817</v>
+        <v>56522</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -27300,28 +27276,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>561023</v>
+        <v>561067</v>
       </c>
       <c r="R205" t="n">
-        <v>6627575</v>
+        <v>6627551</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27345,22 +27324,27 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-03-28</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Sprang över Skogsmursvägen  helvit</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27369,14 +27353,8 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
-      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
@@ -27392,38 +27370,38 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126415504</t>
+          <t>https://artportalen.se/Sighting/91949709</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135660351</v>
+        <v>135589893</v>
       </c>
       <c r="B206" t="n">
-        <v>58846</v>
+        <v>56713</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -27431,14 +27409,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N206" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -27446,17 +27431,17 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Skogsmursvägen, Ramnäs, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>561052</v>
+        <v>561272</v>
       </c>
       <c r="R206" t="n">
-        <v>6627613</v>
+        <v>6627729</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -27480,27 +27465,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -27509,13 +27489,17 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>Myrholme</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr"/>
@@ -27532,63 +27516,70 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135660351</t>
+          <t>https://artportalen.se/Sighting/135589893</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118334109</v>
+        <v>135649870</v>
       </c>
       <c r="B207" t="n">
-        <v>99035</v>
+        <v>56713</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>561057</v>
+        <v>561104</v>
       </c>
       <c r="R207" t="n">
-        <v>6627592</v>
+        <v>6627266</v>
       </c>
       <c r="S207" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -27612,22 +27603,27 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Älgko med fjolårsunge</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -27658,16 +27654,16 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118334109</t>
+          <t>https://artportalen.se/Sighting/135649870</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126416641</v>
+        <v>126415504</v>
       </c>
       <c r="B208" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27675,21 +27671,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -27697,24 +27693,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>561018</v>
+        <v>561023</v>
       </c>
       <c r="R208" t="n">
-        <v>6627875</v>
+        <v>6627575</v>
       </c>
       <c r="S208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -27762,12 +27762,13 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr"/>
@@ -27784,16 +27785,16 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416641</t>
+          <t>https://artportalen.se/Sighting/126415504</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>135071078</v>
+        <v>135660351</v>
       </c>
       <c r="B209" t="n">
-        <v>99186</v>
+        <v>58846</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -27801,51 +27802,54 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursvägen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>561117</v>
+        <v>561052</v>
       </c>
       <c r="R209" t="n">
-        <v>6627574</v>
+        <v>6627613</v>
       </c>
       <c r="S209" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -27869,22 +27873,27 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Hoppandes över vägen. Hoppade sen ner i bäcken.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27893,12 +27902,13 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr"/>
@@ -27915,16 +27925,16 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135071078</t>
+          <t>https://artportalen.se/Sighting/135660351</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135147368</v>
+        <v>118334109</v>
       </c>
       <c r="B210" t="n">
-        <v>99186</v>
+        <v>99035</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -27954,11 +27964,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K210" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -27966,17 +27971,17 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogsmursskogen, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>561051</v>
+        <v>561057</v>
       </c>
       <c r="R210" t="n">
-        <v>6627607</v>
+        <v>6627592</v>
       </c>
       <c r="S210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28000,22 +28005,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28026,6 +28031,11 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
@@ -28041,16 +28051,16 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147368</t>
+          <t>https://artportalen.se/Sighting/118334109</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135147426</v>
+        <v>126416641</v>
       </c>
       <c r="B211" t="n">
-        <v>99186</v>
+        <v>99035</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -28077,7 +28087,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -28087,17 +28097,17 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>561010</v>
+        <v>561018</v>
       </c>
       <c r="R211" t="n">
-        <v>6627744</v>
+        <v>6627875</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28121,22 +28131,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28167,13 +28177,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147426</t>
+          <t>https://artportalen.se/Sighting/126416641</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135147597</v>
+        <v>135071078</v>
       </c>
       <c r="B212" t="n">
         <v>99186</v>
@@ -28203,7 +28213,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -28222,13 +28232,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>561003</v>
+        <v>561117</v>
       </c>
       <c r="R212" t="n">
-        <v>6627860</v>
+        <v>6627574</v>
       </c>
       <c r="S212" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28252,22 +28262,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28298,13 +28308,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147597</t>
+          <t>https://artportalen.se/Sighting/135071078</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135147621</v>
+        <v>135147368</v>
       </c>
       <c r="B213" t="n">
         <v>99186</v>
@@ -28353,13 +28363,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>561005</v>
+        <v>561051</v>
       </c>
       <c r="R213" t="n">
-        <v>6627859</v>
+        <v>6627607</v>
       </c>
       <c r="S213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28388,7 +28398,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -28398,7 +28408,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28409,11 +28419,6 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
@@ -28429,68 +28434,63 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135147621</t>
+          <t>https://artportalen.se/Sighting/135147368</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>116192832</v>
+        <v>135147426</v>
       </c>
       <c r="B214" t="n">
-        <v>99118</v>
+        <v>99186</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogen öster om Murmossen, Ramnäs, Vstm, Skogen öster om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>561001</v>
+        <v>561010</v>
       </c>
       <c r="R214" t="n">
-        <v>6627609</v>
+        <v>6627744</v>
       </c>
       <c r="S214" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -28514,22 +28514,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -28560,70 +28560,68 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192832</t>
+          <t>https://artportalen.se/Sighting/135147426</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>116196922</v>
+        <v>135147597</v>
       </c>
       <c r="B215" t="n">
-        <v>99118</v>
+        <v>99186</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>561103</v>
+        <v>561003</v>
       </c>
       <c r="R215" t="n">
-        <v>6627492</v>
+        <v>6627860</v>
       </c>
       <c r="S215" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -28647,22 +28645,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -28671,13 +28669,12 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
-      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr"/>
@@ -28694,38 +28691,38 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116196922</t>
+          <t>https://artportalen.se/Sighting/135147597</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>116377628</v>
+        <v>135147621</v>
       </c>
       <c r="B216" t="n">
-        <v>99118</v>
+        <v>99186</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -28735,33 +28732,27 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>560998</v>
+        <v>561005</v>
       </c>
       <c r="R216" t="n">
-        <v>6627569</v>
+        <v>6627859</v>
       </c>
       <c r="S216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -28785,22 +28776,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28809,7 +28800,6 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -28832,13 +28822,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116377628</t>
+          <t>https://artportalen.se/Sighting/135147621</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>123329692</v>
+        <v>116192832</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -28868,12 +28858,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -28881,25 +28871,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr"/>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen V om Murmossen, Ramnäs, Vstm sn , Skogen V om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>561099</v>
+        <v>561001</v>
       </c>
       <c r="R217" t="n">
-        <v>6627492</v>
+        <v>6627609</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -28923,12 +28907,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28937,18 +28931,12 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr"/>
@@ -28965,16 +28953,16 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123329692</t>
+          <t>https://artportalen.se/Sighting/116192832</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>132660822</v>
+        <v>116196922</v>
       </c>
       <c r="B218" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -29001,12 +28989,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -29014,19 +29002,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>560999</v>
+        <v>561103</v>
       </c>
       <c r="R218" t="n">
-        <v>6627568</v>
+        <v>6627492</v>
       </c>
       <c r="S218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29050,27 +29040,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29079,6 +29064,7 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -29101,54 +29087,74 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132660822</t>
+          <t>https://artportalen.se/Sighting/116196922</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>4221674</v>
+        <v>116377628</v>
       </c>
       <c r="B219" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Murmossen, Ramnäs sn, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>561035</v>
+        <v>560998</v>
       </c>
       <c r="R219" t="n">
-        <v>6627874</v>
+        <v>6627569</v>
       </c>
       <c r="S219" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29172,12 +29178,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29186,76 +29202,97 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>Tallskog/moränmark</t>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4221674</t>
+          <t>https://artportalen.se/Sighting/116377628</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>4225188</v>
+        <v>123329692</v>
       </c>
       <c r="B220" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Salsmossen SV, Vstm</t>
+          <t>Salsmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>561108</v>
+        <v>561099</v>
       </c>
       <c r="R220" t="n">
-        <v>6627497</v>
+        <v>6627492</v>
       </c>
       <c r="S220" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29279,17 +29316,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2012-07-10</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>sparsam</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29298,84 +29330,96 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Barrskog med marktäcke av mossa och blåbärsris</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4225188</t>
+          <t>https://artportalen.se/Sighting/123329692</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>99086346</v>
+        <v>132660822</v>
       </c>
       <c r="B221" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm sn , Skogen Ö om Murmossen, Ramnäs, Vstm sn , Vstm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>561003</v>
+        <v>560999</v>
       </c>
       <c r="R221" t="n">
-        <v>6627635</v>
+        <v>6627568</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29399,12 +29443,27 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Växer i slänten i en mossig flerskiktad granskog i närheten av sumpskog</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29413,9 +29472,13 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
@@ -29431,13 +29494,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99086346</t>
+          <t>https://artportalen.se/Sighting/132660822</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>104578243</v>
+        <v>4221674</v>
       </c>
       <c r="B222" t="n">
         <v>97983</v>
@@ -29466,27 +29529,19 @@
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Murmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>560987</v>
+        <v>561035</v>
       </c>
       <c r="R222" t="n">
-        <v>6627629</v>
+        <v>6627874</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29510,12 +29565,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2009-07-05</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29524,36 +29579,35 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>Tallskog/moränmark</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104578243</t>
+          <t>https://artportalen.se/Sighting/4221674</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>116192263</v>
+        <v>4225188</v>
       </c>
       <c r="B223" t="n">
         <v>97983</v>
@@ -29581,29 +29635,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Salsmossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>560991</v>
+        <v>561108</v>
       </c>
       <c r="R223" t="n">
-        <v>6627626</v>
+        <v>6627497</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -29627,22 +29672,17 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2012-07-10</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2012-07-10</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>sparsam</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -29654,32 +29694,32 @@
       <c r="AG223" t="b">
         <v>0</v>
       </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116192263</t>
+          <t>https://artportalen.se/Sighting/4225188</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>126413111</v>
+        <v>99086346</v>
       </c>
       <c r="B224" t="n">
         <v>97983</v>
@@ -29707,26 +29747,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen Ö om Murmossen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>561017</v>
+        <v>561003</v>
       </c>
       <c r="R224" t="n">
-        <v>6627814</v>
+        <v>6627635</v>
       </c>
       <c r="S224" t="n">
         <v>5</v>
@@ -29753,22 +29792,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29777,6 +29806,7 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -29794,13 +29824,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413111</t>
+          <t>https://artportalen.se/Sighting/99086346</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>126413356</v>
+        <v>104578243</v>
       </c>
       <c r="B225" t="n">
         <v>97983</v>
@@ -29828,29 +29858,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>561013</v>
+        <v>560987</v>
       </c>
       <c r="R225" t="n">
-        <v>6627677</v>
+        <v>6627629</v>
       </c>
       <c r="S225" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -29874,22 +29903,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2022-11-10</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -29898,6 +29917,7 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
@@ -29920,13 +29940,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413356</t>
+          <t>https://artportalen.se/Sighting/104578243</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>126416592</v>
+        <v>116192263</v>
       </c>
       <c r="B226" t="n">
         <v>97983</v>
@@ -29956,7 +29976,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -29966,17 +29986,17 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm , Murmosseskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>561027</v>
+        <v>560991</v>
       </c>
       <c r="R226" t="n">
-        <v>6627858</v>
+        <v>6627626</v>
       </c>
       <c r="S226" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30000,22 +30020,22 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30026,6 +30046,11 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
@@ -30041,13 +30066,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126416592</t>
+          <t>https://artportalen.se/Sighting/116192263</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128162622</v>
+        <v>126413111</v>
       </c>
       <c r="B227" t="n">
         <v>97983</v>
@@ -30077,7 +30102,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -30087,17 +30112,17 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>561012</v>
+        <v>561017</v>
       </c>
       <c r="R227" t="n">
-        <v>6627671</v>
+        <v>6627814</v>
       </c>
       <c r="S227" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30121,22 +30146,22 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30147,11 +30172,6 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -30167,16 +30187,16 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162622</t>
+          <t>https://artportalen.se/Sighting/126413111</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133764984</v>
+        <v>126413356</v>
       </c>
       <c r="B228" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -30203,7 +30223,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -30213,17 +30233,17 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>561227</v>
+        <v>561013</v>
       </c>
       <c r="R228" t="n">
-        <v>6627267</v>
+        <v>6627677</v>
       </c>
       <c r="S228" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30247,22 +30267,22 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30293,16 +30313,16 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133764984</t>
+          <t>https://artportalen.se/Sighting/126413356</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>112959278</v>
+        <v>126416592</v>
       </c>
       <c r="B229" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -30310,16 +30330,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -30327,28 +30347,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmursskogen, Ramnäs, Vstm, Skogsmursskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>561019</v>
+        <v>561027</v>
       </c>
       <c r="R229" t="n">
-        <v>6627490</v>
+        <v>6627858</v>
       </c>
       <c r="S229" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30372,12 +30393,22 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30386,7 +30417,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -30404,16 +30434,16 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112959278</t>
+          <t>https://artportalen.se/Sighting/126416592</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>134063381</v>
+        <v>128162622</v>
       </c>
       <c r="B230" t="n">
-        <v>99472</v>
+        <v>97983</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -30421,16 +30451,16 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>222812</v>
+        <v>221945</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -30438,25 +30468,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
+          <t>Skogen Ö om Murmossen, Skogen Ö om Murmossen, Vstm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>560964</v>
+        <v>561012</v>
       </c>
       <c r="R230" t="n">
-        <v>6627632</v>
+        <v>6627671</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30480,22 +30514,22 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -30526,16 +30560,16 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134063381</t>
+          <t>https://artportalen.se/Sighting/128162622</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>5979250</v>
+        <v>133764984</v>
       </c>
       <c r="B231" t="n">
-        <v>99038</v>
+        <v>98060</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -30543,47 +30577,46 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Salsmosseskogen, Ramnäd, Salsmosseskogen, Ramnäd, Vstm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>560984</v>
+        <v>561227</v>
       </c>
       <c r="R231" t="n">
-        <v>6627735</v>
+        <v>6627267</v>
       </c>
       <c r="S231" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30607,12 +30640,22 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30624,35 +30667,35 @@
       <c r="AG231" t="b">
         <v>0</v>
       </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979250</t>
+          <t>https://artportalen.se/Sighting/133764984</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>5979251</v>
+        <v>136175493</v>
       </c>
       <c r="B232" t="n">
-        <v>99038</v>
+        <v>98156</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -30660,47 +30703,53 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>560967</v>
+        <v>561037</v>
       </c>
       <c r="R232" t="n">
-        <v>6627698</v>
+        <v>6627842</v>
       </c>
       <c r="S232" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -30724,12 +30773,22 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -30738,38 +30797,39 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979251</t>
+          <t>https://artportalen.se/Sighting/136175493</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>5979254</v>
+        <v>112959278</v>
       </c>
       <c r="B233" t="n">
-        <v>99038</v>
+        <v>97986</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -30777,44 +30837,42 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>560937</v>
+        <v>561019</v>
       </c>
       <c r="R233" t="n">
-        <v>6627972</v>
+        <v>6627490</v>
       </c>
       <c r="S233" t="n">
         <v>25</v>
@@ -30841,12 +30899,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -30855,38 +30913,34 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
+      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5979254</t>
+          <t>https://artportalen.se/Sighting/112959278</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>5979255</v>
+        <v>134063381</v>
       </c>
       <c r="B234" t="n">
-        <v>99038</v>
+        <v>99472</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -30894,47 +30948,42 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>223597</v>
+        <v>222812</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Murmossen, Vstm</t>
+          <t>Murmosseskogen, Ramnäs, Murmosseskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>560943</v>
+        <v>560964</v>
       </c>
       <c r="R234" t="n">
-        <v>6627939</v>
+        <v>6627632</v>
       </c>
       <c r="S234" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -30958,12 +31007,22 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2009-07-05</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -30975,24 +31034,492 @@
       <c r="AG234" t="b">
         <v>0</v>
       </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134063381</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>5979250</v>
+      </c>
+      <c r="B235" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>560984</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6627735</v>
+      </c>
+      <c r="S235" t="n">
+        <v>25</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979250</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>5979251</v>
+      </c>
+      <c r="B236" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>560967</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6627698</v>
+      </c>
+      <c r="S236" t="n">
+        <v>25</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979251</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>5979254</v>
+      </c>
+      <c r="B237" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>560937</v>
+      </c>
+      <c r="R237" t="n">
+        <v>6627972</v>
+      </c>
+      <c r="S237" t="n">
+        <v>25</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5979254</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>5979255</v>
+      </c>
+      <c r="B238" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Murmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>560943</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6627939</v>
+      </c>
+      <c r="S238" t="n">
+        <v>25</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2009-07-05</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5979255</t>
         </is>
@@ -31233,6 +31760,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>136175493</v>
       </c>
       <c r="B232" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136014972</v>
       </c>
       <c r="B74" t="n">
-        <v>56857</v>
+        <v>56861</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>136172601</v>
       </c>
       <c r="B75" t="n">
-        <v>56857</v>
+        <v>56861</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>135570571</v>
       </c>
       <c r="B121" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>135570663</v>
       </c>
       <c r="B158" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>136168846</v>
       </c>
       <c r="B159" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>135570691</v>
       </c>
       <c r="B163" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>136168858</v>
       </c>
       <c r="B164" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>136014966</v>
       </c>
       <c r="B195" t="n">
-        <v>56862</v>
+        <v>56866</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>136014802</v>
       </c>
       <c r="B201" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>136171058</v>
       </c>
       <c r="B202" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>136014962</v>
       </c>
       <c r="B206" t="n">
-        <v>56864</v>
+        <v>56868</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>136171108</v>
       </c>
       <c r="B207" t="n">
-        <v>56864</v>
+        <v>56868</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>135649870</v>
       </c>
       <c r="B210" t="n">
-        <v>56714</v>
+        <v>56718</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>135660351</v>
       </c>
       <c r="B212" t="n">
-        <v>58847</v>
+        <v>58851</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136014972</v>
       </c>
       <c r="B74" t="n">
-        <v>56861</v>
+        <v>56862</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>136172601</v>
       </c>
       <c r="B75" t="n">
-        <v>56861</v>
+        <v>56862</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>135570571</v>
       </c>
       <c r="B121" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>135570663</v>
       </c>
       <c r="B158" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>136168846</v>
       </c>
       <c r="B159" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>135570691</v>
       </c>
       <c r="B163" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>136168858</v>
       </c>
       <c r="B164" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>136014966</v>
       </c>
       <c r="B195" t="n">
-        <v>56866</v>
+        <v>56867</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>136014802</v>
       </c>
       <c r="B201" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>136171058</v>
       </c>
       <c r="B202" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>136014962</v>
       </c>
       <c r="B206" t="n">
-        <v>56868</v>
+        <v>56869</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>136171108</v>
       </c>
       <c r="B207" t="n">
-        <v>56868</v>
+        <v>56869</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>135660351</v>
       </c>
       <c r="B212" t="n">
-        <v>58851</v>
+        <v>58852</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136014972</v>
       </c>
       <c r="B74" t="n">
-        <v>56862</v>
+        <v>56867</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>136172601</v>
       </c>
       <c r="B75" t="n">
-        <v>56862</v>
+        <v>56867</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>135570571</v>
       </c>
       <c r="B121" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>135570663</v>
       </c>
       <c r="B158" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>136168846</v>
       </c>
       <c r="B159" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>135570691</v>
       </c>
       <c r="B163" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>136168858</v>
       </c>
       <c r="B164" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>136014966</v>
       </c>
       <c r="B195" t="n">
-        <v>56867</v>
+        <v>56872</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>136014802</v>
       </c>
       <c r="B201" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>136171058</v>
       </c>
       <c r="B202" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>136014962</v>
       </c>
       <c r="B206" t="n">
-        <v>56869</v>
+        <v>56874</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>136171108</v>
       </c>
       <c r="B207" t="n">
-        <v>56869</v>
+        <v>56874</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136014972</v>
       </c>
       <c r="B74" t="n">
-        <v>56867</v>
+        <v>56880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>136172601</v>
       </c>
       <c r="B75" t="n">
-        <v>56867</v>
+        <v>56880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>136168846</v>
       </c>
       <c r="B159" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>136168858</v>
       </c>
       <c r="B164" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>136014966</v>
       </c>
       <c r="B195" t="n">
-        <v>56872</v>
+        <v>56885</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>136014802</v>
       </c>
       <c r="B201" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>136171058</v>
       </c>
       <c r="B202" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>136014962</v>
       </c>
       <c r="B206" t="n">
-        <v>56874</v>
+        <v>56887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>136171108</v>
       </c>
       <c r="B207" t="n">
-        <v>56874</v>
+        <v>56887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>

--- a/artfynd/A 39697-2025 artfynd.xlsx
+++ b/artfynd/A 39697-2025 artfynd.xlsx
@@ -4946,7 +4946,7 @@
         <v>136117990</v>
       </c>
       <c r="B37" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>136175493</v>
       </c>
       <c r="B235" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
